--- a/plot/data/raw/expert_rating_workbooks/专家3-专家评分——统计版.xlsx
+++ b/plot/data/raw/expert_rating_workbooks/专家3-专家评分——统计版.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8055" firstSheet="3" activeTab="10"/>
+    <workbookView windowWidth="25600" windowHeight="12790" firstSheet="3" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="P" sheetId="1" r:id="rId1"/>
@@ -318,7 +318,7 @@
     <t>总正确率</t>
   </si>
   <si>
-    <t>65/120</t>
+    <t>65/140</t>
   </si>
   <si>
     <t>A1汇总</t>
@@ -1759,16 +1759,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AB92"/>
-  <sheetFormatPr defaultColWidth="9.64601769911504" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.64545454545454" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="4.52212389380531" style="31" customWidth="1"/>
-    <col min="2" max="8" width="6.52212389380531" customWidth="1"/>
-    <col min="9" max="9" width="10.5663716814159" customWidth="1"/>
-    <col min="10" max="10" width="12.7964601769912" style="34"/>
-    <col min="11" max="25" width="12.7964601769912"/>
-    <col min="26" max="26" width="12.9380530973451" customWidth="1"/>
-    <col min="27" max="27" width="12.7964601769912" style="34"/>
-    <col min="28" max="28" width="19.4424778761062" customWidth="1"/>
+    <col min="1" max="1" width="4.51818181818182" style="31" customWidth="1"/>
+    <col min="2" max="8" width="6.51818181818182" customWidth="1"/>
+    <col min="9" max="9" width="10.5636363636364" customWidth="1"/>
+    <col min="10" max="10" width="12.8" style="34"/>
+    <col min="11" max="25" width="12.8"/>
+    <col min="26" max="26" width="12.9363636363636" customWidth="1"/>
+    <col min="27" max="27" width="12.8" style="34"/>
+    <col min="28" max="28" width="19.4454545454545" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:28">
@@ -1977,7 +1977,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" customHeight="1" spans="1:28">
+    <row r="4" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A4" s="13"/>
       <c r="B4" s="14">
         <v>4</v>
@@ -2063,7 +2063,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" customHeight="1" spans="1:28">
+    <row r="5" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A5" s="13"/>
       <c r="B5" s="14">
         <v>5</v>
@@ -2149,7 +2149,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:28">
+    <row r="6" ht="13.5" customHeight="1" spans="1:28">
       <c r="A6" s="15"/>
       <c r="B6" s="14">
         <v>14</v>
@@ -2235,7 +2235,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:28">
+    <row r="7" ht="13.5" customHeight="1" spans="1:28">
       <c r="A7" s="15"/>
       <c r="B7" s="14">
         <v>15</v>
@@ -2321,7 +2321,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:28">
+    <row r="8" ht="13.5" customHeight="1" spans="1:28">
       <c r="A8" s="15"/>
       <c r="B8" s="14">
         <v>16</v>
@@ -2407,7 +2407,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:28">
+    <row r="9" ht="13.5" customHeight="1" spans="1:28">
       <c r="A9" s="15"/>
       <c r="B9" s="14">
         <v>17</v>
@@ -2493,7 +2493,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:28">
+    <row r="10" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A10" s="9" t="s">
         <v>31</v>
       </c>
@@ -2581,7 +2581,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:28">
+    <row r="11" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A11" s="13"/>
       <c r="B11" s="14">
         <v>2</v>
@@ -2667,7 +2667,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:28">
+    <row r="12" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A12" s="13"/>
       <c r="B12" s="14">
         <v>6</v>
@@ -2753,7 +2753,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:28">
+    <row r="13" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A13" s="13"/>
       <c r="B13" s="14">
         <v>7</v>
@@ -2839,7 +2839,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:28">
+    <row r="14" ht="13.5" customHeight="1" spans="1:28">
       <c r="A14" s="15"/>
       <c r="B14" s="14">
         <v>17</v>
@@ -2925,7 +2925,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:28">
+    <row r="15" ht="13.5" customHeight="1" spans="1:28">
       <c r="A15" s="15"/>
       <c r="B15" s="14">
         <v>26</v>
@@ -3011,7 +3011,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:28">
+    <row r="16" ht="13.5" customHeight="1" spans="1:28">
       <c r="A16" s="15"/>
       <c r="B16" s="14">
         <v>27</v>
@@ -3097,7 +3097,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:28">
+    <row r="17" ht="13.5" customHeight="1" spans="1:28">
       <c r="A17" s="15"/>
       <c r="B17" s="14">
         <v>28</v>
@@ -3183,7 +3183,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="1:28">
+    <row r="18" ht="13.5" customHeight="1" spans="1:28">
       <c r="A18" s="15"/>
       <c r="B18" s="14">
         <v>29</v>
@@ -3269,7 +3269,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="1:28">
+    <row r="19" ht="13.5" customHeight="1" spans="1:28">
       <c r="A19" s="15"/>
       <c r="B19" s="14">
         <v>30</v>
@@ -3355,7 +3355,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="1:28">
+    <row r="20" ht="13.5" customHeight="1" spans="1:28">
       <c r="A20" s="15"/>
       <c r="B20" s="14">
         <v>31</v>
@@ -3441,7 +3441,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="1:28">
+    <row r="21" ht="13.5" customHeight="1" spans="1:28">
       <c r="A21" s="15"/>
       <c r="B21" s="14">
         <v>32</v>
@@ -3527,7 +3527,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="1:28">
+    <row r="22" ht="13.5" customHeight="1" spans="1:28">
       <c r="A22" s="15"/>
       <c r="B22" s="14">
         <v>33</v>
@@ -3613,7 +3613,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="1:28">
+    <row r="23" ht="13.5" customHeight="1" spans="1:28">
       <c r="A23" s="15"/>
       <c r="B23" s="14">
         <v>34</v>
@@ -3699,7 +3699,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="1:28">
+    <row r="24" ht="13.5" customHeight="1" spans="1:28">
       <c r="A24" s="15"/>
       <c r="B24" s="14">
         <v>35</v>
@@ -3785,7 +3785,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="1:28">
+    <row r="25" ht="13.5" customHeight="1" spans="1:28">
       <c r="A25" s="15"/>
       <c r="B25" s="14">
         <v>36</v>
@@ -3871,7 +3871,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="1:28">
+    <row r="26" ht="13.5" customHeight="1" spans="1:28">
       <c r="A26" s="15"/>
       <c r="B26" s="14">
         <v>37</v>
@@ -3957,7 +3957,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="1:28">
+    <row r="27" ht="13.5" customHeight="1" spans="1:28">
       <c r="A27" s="15"/>
       <c r="B27" s="14">
         <v>38</v>
@@ -4043,7 +4043,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="1:28">
+    <row r="28" ht="13.5" customHeight="1" spans="1:28">
       <c r="A28" s="30" t="s">
         <v>32</v>
       </c>
@@ -4131,7 +4131,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="1:28">
+    <row r="29" ht="13.5" customHeight="1" spans="1:28">
       <c r="A29" s="15"/>
       <c r="B29" s="10">
         <v>2</v>
@@ -4217,7 +4217,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="1:28">
+    <row r="30" ht="13.5" customHeight="1" spans="1:28">
       <c r="A30" s="15"/>
       <c r="B30" s="10">
         <v>3</v>
@@ -4303,7 +4303,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="1:28">
+    <row r="31" ht="13.5" customHeight="1" spans="1:28">
       <c r="A31" s="15"/>
       <c r="B31" s="10">
         <v>4</v>
@@ -4389,7 +4389,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="1:28">
+    <row r="32" ht="13.5" customHeight="1" spans="1:28">
       <c r="A32" s="15"/>
       <c r="B32" s="10">
         <v>5</v>
@@ -4475,7 +4475,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" customHeight="1" spans="1:28">
+    <row r="33" ht="13.5" customHeight="1" spans="1:28">
       <c r="A33" s="15"/>
       <c r="B33" s="10">
         <v>6</v>
@@ -4561,7 +4561,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="34" customHeight="1" spans="1:28">
+    <row r="34" ht="13.5" customHeight="1" spans="1:28">
       <c r="A34" s="15"/>
       <c r="B34" s="10">
         <v>7</v>
@@ -4647,7 +4647,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="35" customHeight="1" spans="1:28">
+    <row r="35" ht="13.5" customHeight="1" spans="1:28">
       <c r="A35" s="15"/>
       <c r="B35" s="10">
         <v>8</v>
@@ -4733,7 +4733,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="36" customHeight="1" spans="1:28">
+    <row r="36" ht="13.5" customHeight="1" spans="1:28">
       <c r="A36" s="15"/>
       <c r="B36" s="10">
         <v>9</v>
@@ -4819,7 +4819,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="37" customHeight="1" spans="1:28">
+    <row r="37" ht="13.5" customHeight="1" spans="1:28">
       <c r="A37" s="15"/>
       <c r="B37" s="10">
         <v>10</v>
@@ -4905,7 +4905,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="38" customHeight="1" spans="1:28">
+    <row r="38" ht="13.5" customHeight="1" spans="1:28">
       <c r="A38" s="15"/>
       <c r="B38" s="10">
         <v>11</v>
@@ -4991,7 +4991,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="39" customHeight="1" spans="1:28">
+    <row r="39" ht="13.5" customHeight="1" spans="1:28">
       <c r="A39" s="15"/>
       <c r="B39" s="10">
         <v>12</v>
@@ -5077,7 +5077,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="40" customHeight="1" spans="1:28">
+    <row r="40" ht="13.5" customHeight="1" spans="1:28">
       <c r="A40" s="15"/>
       <c r="B40" s="10">
         <v>13</v>
@@ -5163,7 +5163,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="41" customHeight="1" spans="1:28">
+    <row r="41" ht="13.5" customHeight="1" spans="1:28">
       <c r="A41" s="15"/>
       <c r="B41" s="10">
         <v>14</v>
@@ -5249,7 +5249,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="42" customHeight="1" spans="1:28">
+    <row r="42" ht="13.5" customHeight="1" spans="1:28">
       <c r="A42" s="15" t="s">
         <v>33</v>
       </c>
@@ -5337,7 +5337,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="43" customHeight="1" spans="1:28">
+    <row r="43" ht="13.5" customHeight="1" spans="1:28">
       <c r="A43" s="15"/>
       <c r="B43" s="14">
         <v>8</v>
@@ -5423,7 +5423,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="44" customHeight="1" spans="1:28">
+    <row r="44" ht="13.5" customHeight="1" spans="1:28">
       <c r="A44" s="24"/>
       <c r="B44" s="14">
         <v>9</v>
@@ -5509,7 +5509,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="45" customHeight="1" spans="1:28">
+    <row r="45" ht="13.5" customHeight="1" spans="1:28">
       <c r="A45" s="20" t="s">
         <v>34</v>
       </c>
@@ -5597,7 +5597,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="46" customHeight="1" spans="1:28">
+    <row r="46" ht="13.5" customHeight="1" spans="1:28">
       <c r="A46" s="20"/>
       <c r="B46" s="21">
         <v>3</v>
@@ -5683,7 +5683,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="47" customHeight="1" spans="1:28">
+    <row r="47" ht="13.5" customHeight="1" spans="1:28">
       <c r="A47" s="20"/>
       <c r="B47" s="21">
         <v>4</v>
@@ -5769,7 +5769,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="48" customHeight="1" spans="1:28">
+    <row r="48" ht="13.5" customHeight="1" spans="1:28">
       <c r="A48" s="20"/>
       <c r="B48" s="21">
         <v>5</v>
@@ -5854,7 +5854,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="49" customHeight="1" spans="1:28">
+    <row r="49" ht="13.5" customHeight="1" spans="1:28">
       <c r="A49" s="20"/>
       <c r="B49" s="21">
         <v>6</v>
@@ -5940,7 +5940,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="50" customHeight="1" spans="1:28">
+    <row r="50" ht="13.5" customHeight="1" spans="1:28">
       <c r="A50" s="20"/>
       <c r="B50" s="21">
         <v>7</v>
@@ -6026,7 +6026,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="51" customHeight="1" spans="1:28">
+    <row r="51" ht="13.5" customHeight="1" spans="1:28">
       <c r="A51" s="20"/>
       <c r="B51" s="21">
         <v>8</v>
@@ -6112,7 +6112,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="52" customHeight="1" spans="1:28">
+    <row r="52" ht="13.5" customHeight="1" spans="1:28">
       <c r="A52" s="28"/>
       <c r="B52" s="22">
         <v>12</v>
@@ -6198,7 +6198,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="53" customHeight="1" spans="1:28">
+    <row r="53" ht="13.5" customHeight="1" spans="1:28">
       <c r="B53" s="23" t="s">
         <v>35</v>
       </c>
@@ -6311,7 +6311,7 @@
         <v>37</v>
       </c>
       <c r="C54" s="12">
-        <f t="shared" ref="C54:Z54" si="4">_xlfn.STDEV.S(C3:C52)</f>
+        <f t="shared" ref="C54:AA54" si="4">_xlfn.STDEV.S(C3:C52)</f>
         <v>0.340467865366085</v>
       </c>
       <c r="D54" s="12">
@@ -6407,7 +6407,7 @@
         <v>0.385449644663773</v>
       </c>
       <c r="AA54" s="12">
-        <f>_xlfn.STDEV.S(AA3:AA52)</f>
+        <f t="shared" si="4"/>
         <v>2.69913062345063</v>
       </c>
       <c r="AB54" s="11" t="s">
@@ -7542,13 +7542,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AA78"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.02727272727273" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="24" width="12.7964601769912"/>
-    <col min="26" max="27" width="12.7964601769912"/>
+    <col min="2" max="24" width="12.8"/>
+    <col min="26" max="27" width="12.8"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" customHeight="1" spans="1:27">
+    <row r="1" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -7716,7 +7716,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" customHeight="1" spans="1:27">
+    <row r="3" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A3" s="13"/>
       <c r="B3" s="14">
         <v>4</v>
@@ -7799,7 +7799,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" customHeight="1" spans="1:27">
+    <row r="4" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A4" s="13"/>
       <c r="B4" s="14">
         <v>5</v>
@@ -7882,7 +7882,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:27">
+    <row r="5" ht="13.5" customHeight="1" spans="1:27">
       <c r="A5" s="15"/>
       <c r="B5" s="14">
         <v>14</v>
@@ -7965,7 +7965,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:27">
+    <row r="6" ht="13.5" customHeight="1" spans="1:27">
       <c r="A6" s="15"/>
       <c r="B6" s="14">
         <v>15</v>
@@ -8048,7 +8048,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:27">
+    <row r="7" ht="13.5" customHeight="1" spans="1:27">
       <c r="A7" s="15"/>
       <c r="B7" s="14">
         <v>16</v>
@@ -8131,7 +8131,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:27">
+    <row r="8" ht="13.5" customHeight="1" spans="1:27">
       <c r="A8" s="15"/>
       <c r="B8" s="14">
         <v>17</v>
@@ -8214,7 +8214,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="9" customFormat="1" customHeight="1" spans="1:27">
+    <row r="9" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A9" s="15"/>
       <c r="B9" s="16">
         <v>18</v>
@@ -8297,7 +8297,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="10" customFormat="1" customHeight="1" spans="1:27">
+    <row r="10" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A10" s="15"/>
       <c r="B10" s="16">
         <v>19</v>
@@ -8380,7 +8380,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" customFormat="1" customHeight="1" spans="1:27">
+    <row r="11" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A11" s="15"/>
       <c r="B11" s="16">
         <v>20</v>
@@ -8463,7 +8463,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" customFormat="1" customHeight="1" spans="1:27">
+    <row r="12" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="C12">
         <f>AVERAGE(C2:C11)</f>
         <v>4.9</v>
@@ -8565,8 +8565,8 @@
         <v>67.9</v>
       </c>
     </row>
-    <row r="13" customHeight="1"/>
-    <row r="14" customHeight="1" spans="1:27">
+    <row r="13" ht="13.5" customHeight="1"/>
+    <row r="14" ht="13.5" customHeight="1" spans="1:27">
       <c r="A14" s="17" t="s">
         <v>134</v>
       </c>
@@ -8651,7 +8651,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:27">
+    <row r="15" ht="13.5" customHeight="1" spans="1:27">
       <c r="A15" s="17"/>
       <c r="B15" s="14">
         <v>8</v>
@@ -8734,7 +8734,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:27">
+    <row r="16" ht="13.5" customHeight="1" spans="1:27">
       <c r="A16" s="27"/>
       <c r="B16" s="14">
         <v>9</v>
@@ -8817,7 +8817,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:27">
+    <row r="17" ht="13.5" customHeight="1" spans="1:27">
       <c r="A17" s="17"/>
       <c r="B17" s="16">
         <v>10</v>
@@ -8900,7 +8900,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="1:27">
+    <row r="18" ht="13.5" customHeight="1" spans="1:27">
       <c r="A18" s="17"/>
       <c r="B18" s="16">
         <v>11</v>
@@ -8983,7 +8983,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="1:27">
+    <row r="19" ht="13.5" customHeight="1" spans="1:27">
       <c r="A19" s="17"/>
       <c r="B19" s="16">
         <v>12</v>
@@ -9066,7 +9066,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="1:27">
+    <row r="20" ht="13.5" customHeight="1" spans="1:27">
       <c r="A20" s="20"/>
       <c r="B20" s="21">
         <v>2</v>
@@ -9149,7 +9149,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" customFormat="1" customHeight="1" spans="1:27">
+    <row r="21" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A21" s="20"/>
       <c r="B21" s="21">
         <v>3</v>
@@ -9232,7 +9232,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="22" customFormat="1" customHeight="1" spans="1:27">
+    <row r="22" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A22" s="20"/>
       <c r="B22" s="21">
         <v>4</v>
@@ -9315,7 +9315,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="23" customFormat="1" customHeight="1" spans="1:27">
+    <row r="23" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A23" s="20"/>
       <c r="B23" s="21">
         <v>5</v>
@@ -9397,7 +9397,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="24" customFormat="1" customHeight="1" spans="1:27">
+    <row r="24" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A24" s="20"/>
       <c r="B24" s="21">
         <v>6</v>
@@ -9480,7 +9480,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="25" customFormat="1" customHeight="1" spans="1:27">
+    <row r="25" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A25" s="20"/>
       <c r="B25" s="21">
         <v>7</v>
@@ -9563,7 +9563,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26" customFormat="1" customHeight="1" spans="1:27">
+    <row r="26" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A26" s="20"/>
       <c r="B26" s="21">
         <v>8</v>
@@ -9646,7 +9646,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" customFormat="1" customHeight="1" spans="1:27">
+    <row r="27" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A27" s="28"/>
       <c r="B27" s="22">
         <v>12</v>
@@ -9729,7 +9729,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="28" customFormat="1" customHeight="1" spans="1:27">
+    <row r="28" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A28" s="28"/>
       <c r="B28" s="23">
         <v>20</v>
@@ -9812,7 +9812,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="29" customFormat="1" customHeight="1" spans="1:27">
+    <row r="29" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A29" s="28"/>
       <c r="B29" s="23">
         <v>21</v>
@@ -9895,7 +9895,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" customFormat="1" customHeight="1" spans="1:27">
+    <row r="30" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A30" s="28"/>
       <c r="B30" s="23">
         <v>22</v>
@@ -9978,7 +9978,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="1:27">
+    <row r="31" ht="13.5" customHeight="1" spans="1:27">
       <c r="C31">
         <f>AVERAGE(C14:C30)</f>
         <v>5</v>
@@ -10080,8 +10080,8 @@
         <v>68.3529411764706</v>
       </c>
     </row>
-    <row r="32" customHeight="1"/>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="1:27">
+    <row r="32" ht="13.5" customHeight="1"/>
+    <row r="33" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A33" s="9" t="s">
         <v>135</v>
       </c>
@@ -10166,7 +10166,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="1:27">
+    <row r="34" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A34" s="13"/>
       <c r="B34" s="14">
         <v>2</v>
@@ -10249,7 +10249,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="1:27">
+    <row r="35" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A35" s="13"/>
       <c r="B35" s="14">
         <v>6</v>
@@ -10332,7 +10332,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" s="2" customFormat="1" customHeight="1" spans="1:27">
+    <row r="36" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A36" s="13"/>
       <c r="B36" s="14">
         <v>7</v>
@@ -10415,7 +10415,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" customHeight="1" spans="1:27">
+    <row r="37" ht="13.5" customHeight="1" spans="1:27">
       <c r="A37" s="13"/>
       <c r="B37" s="14">
         <v>17</v>
@@ -10498,7 +10498,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="38" customHeight="1" spans="1:27">
+    <row r="38" ht="13.5" customHeight="1" spans="1:27">
       <c r="A38" s="13"/>
       <c r="B38" s="14">
         <v>26</v>
@@ -10581,7 +10581,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="39" customHeight="1" spans="1:27">
+    <row r="39" ht="13.5" customHeight="1" spans="1:27">
       <c r="A39" s="13"/>
       <c r="B39" s="14">
         <v>27</v>
@@ -10664,7 +10664,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="40" customHeight="1" spans="1:27">
+    <row r="40" ht="13.5" customHeight="1" spans="1:27">
       <c r="A40" s="13"/>
       <c r="B40" s="14">
         <v>28</v>
@@ -10747,7 +10747,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="41" customHeight="1" spans="1:27">
+    <row r="41" ht="13.5" customHeight="1" spans="1:27">
       <c r="A41" s="13"/>
       <c r="B41" s="14">
         <v>29</v>
@@ -10830,7 +10830,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="42" customHeight="1" spans="1:27">
+    <row r="42" ht="13.5" customHeight="1" spans="1:27">
       <c r="A42" s="13"/>
       <c r="B42" s="14">
         <v>30</v>
@@ -10913,7 +10913,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="43" customHeight="1" spans="1:27">
+    <row r="43" ht="13.5" customHeight="1" spans="1:27">
       <c r="A43" s="13"/>
       <c r="B43" s="14">
         <v>31</v>
@@ -10996,7 +10996,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="44" customHeight="1" spans="1:27">
+    <row r="44" ht="13.5" customHeight="1" spans="1:27">
       <c r="A44" s="13"/>
       <c r="B44" s="14">
         <v>32</v>
@@ -11079,7 +11079,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="45" customHeight="1" spans="1:27">
+    <row r="45" ht="13.5" customHeight="1" spans="1:27">
       <c r="A45" s="13"/>
       <c r="B45" s="14">
         <v>33</v>
@@ -11162,7 +11162,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="46" customHeight="1" spans="1:27">
+    <row r="46" ht="13.5" customHeight="1" spans="1:27">
       <c r="A46" s="13"/>
       <c r="B46" s="14">
         <v>34</v>
@@ -11245,7 +11245,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="47" customHeight="1" spans="1:27">
+    <row r="47" ht="13.5" customHeight="1" spans="1:27">
       <c r="A47" s="13"/>
       <c r="B47" s="14">
         <v>35</v>
@@ -11328,7 +11328,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="48" customHeight="1" spans="1:27">
+    <row r="48" ht="13.5" customHeight="1" spans="1:27">
       <c r="A48" s="13"/>
       <c r="B48" s="14">
         <v>36</v>
@@ -11411,7 +11411,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="49" customHeight="1" spans="1:27">
+    <row r="49" ht="13.5" customHeight="1" spans="1:27">
       <c r="A49" s="13"/>
       <c r="B49" s="14">
         <v>37</v>
@@ -11494,7 +11494,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="50" customHeight="1" spans="1:27">
+    <row r="50" ht="13.5" customHeight="1" spans="1:27">
       <c r="A50" s="13"/>
       <c r="B50" s="14">
         <v>38</v>
@@ -11577,7 +11577,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="51" customHeight="1" spans="1:27">
+    <row r="51" ht="13.5" customHeight="1" spans="1:27">
       <c r="A51" s="13"/>
       <c r="B51" s="16">
         <v>44</v>
@@ -11660,7 +11660,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="52" customHeight="1" spans="1:27">
+    <row r="52" ht="13.5" customHeight="1" spans="1:27">
       <c r="A52" s="13"/>
       <c r="B52" s="16">
         <v>45</v>
@@ -11743,7 +11743,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="53" customFormat="1" customHeight="1" spans="1:27">
+    <row r="53" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A53" s="13"/>
       <c r="B53" s="16">
         <v>46</v>
@@ -11826,7 +11826,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="54" customFormat="1" customHeight="1" spans="1:27">
+    <row r="54" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A54" s="13"/>
       <c r="B54" s="16">
         <v>47</v>
@@ -11909,7 +11909,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="55" customFormat="1" customHeight="1" spans="1:27">
+    <row r="55" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A55" s="13"/>
       <c r="B55" s="16">
         <v>48</v>
@@ -11992,7 +11992,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="56" customFormat="1" customHeight="1" spans="1:27">
+    <row r="56" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A56" s="13"/>
       <c r="B56" s="16">
         <v>49</v>
@@ -12075,7 +12075,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="57" customFormat="1" customHeight="1" spans="1:27">
+    <row r="57" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A57" s="13"/>
       <c r="B57" s="16">
         <v>50</v>
@@ -12158,7 +12158,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="58" customFormat="1" customHeight="1" spans="1:27">
+    <row r="58" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A58" s="29"/>
       <c r="B58" s="10"/>
       <c r="C58" s="26">
@@ -12262,7 +12262,7 @@
         <v>69.56</v>
       </c>
     </row>
-    <row r="59" customFormat="1" customHeight="1" spans="1:27">
+    <row r="59" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A59" s="30"/>
       <c r="B59" s="10"/>
       <c r="C59" s="26"/>
@@ -12291,7 +12291,7 @@
       <c r="Z59" s="26"/>
       <c r="AA59" s="12"/>
     </row>
-    <row r="60" customFormat="1" customHeight="1" spans="1:27">
+    <row r="60" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A60" s="30" t="s">
         <v>136</v>
       </c>
@@ -12376,7 +12376,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="61" customFormat="1" customHeight="1" spans="1:27">
+    <row r="61" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A61" s="15"/>
       <c r="B61" s="10">
         <v>2</v>
@@ -12459,7 +12459,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="62" customFormat="1" customHeight="1" spans="1:27">
+    <row r="62" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A62" s="15"/>
       <c r="B62" s="10">
         <v>3</v>
@@ -12542,7 +12542,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="63" customFormat="1" customHeight="1" spans="1:27">
+    <row r="63" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A63" s="15"/>
       <c r="B63" s="10">
         <v>4</v>
@@ -12625,7 +12625,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="64" customFormat="1" customHeight="1" spans="1:27">
+    <row r="64" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A64" s="15"/>
       <c r="B64" s="10">
         <v>5</v>
@@ -12708,7 +12708,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="65" customFormat="1" customHeight="1" spans="1:27">
+    <row r="65" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A65" s="15"/>
       <c r="B65" s="10">
         <v>6</v>
@@ -12791,7 +12791,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="66" customFormat="1" customHeight="1" spans="1:27">
+    <row r="66" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A66" s="15"/>
       <c r="B66" s="10">
         <v>7</v>
@@ -12874,7 +12874,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="67" customFormat="1" customHeight="1" spans="1:27">
+    <row r="67" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A67" s="15"/>
       <c r="B67" s="10">
         <v>8</v>
@@ -12957,7 +12957,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="68" customFormat="1" customHeight="1" spans="1:27">
+    <row r="68" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A68" s="15"/>
       <c r="B68" s="10">
         <v>9</v>
@@ -13040,7 +13040,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="69" customFormat="1" customHeight="1" spans="1:27">
+    <row r="69" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A69" s="15"/>
       <c r="B69" s="10">
         <v>10</v>
@@ -13123,7 +13123,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="70" customFormat="1" customHeight="1" spans="1:27">
+    <row r="70" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A70" s="15"/>
       <c r="B70" s="10">
         <v>11</v>
@@ -13206,7 +13206,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="71" customFormat="1" customHeight="1" spans="1:27">
+    <row r="71" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A71" s="15"/>
       <c r="B71" s="10">
         <v>12</v>
@@ -13289,7 +13289,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="72" customFormat="1" customHeight="1" spans="1:27">
+    <row r="72" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A72" s="15"/>
       <c r="B72" s="10">
         <v>13</v>
@@ -13372,7 +13372,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="73" customFormat="1" customHeight="1" spans="1:27">
+    <row r="73" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A73" s="15"/>
       <c r="B73" s="10">
         <v>14</v>
@@ -13455,7 +13455,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="74" customFormat="1" customHeight="1" spans="1:27">
+    <row r="74" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A74" s="15"/>
       <c r="B74" s="16">
         <v>33</v>
@@ -13538,7 +13538,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="75" customFormat="1" customHeight="1" spans="1:27">
+    <row r="75" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A75" s="15"/>
       <c r="B75" s="16">
         <v>34</v>
@@ -13621,7 +13621,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="76" customFormat="1" customHeight="1" spans="1:27">
+    <row r="76" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A76" s="24"/>
       <c r="B76" s="16">
         <v>35</v>
@@ -13704,7 +13704,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="77" customFormat="1" customHeight="1" spans="1:27">
+    <row r="77" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A77" s="24"/>
       <c r="B77" s="16">
         <v>36</v>
@@ -13906,18 +13906,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AA79"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.02727272727273" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="3" width="12.7964601769912"/>
-    <col min="5" max="6" width="12.7964601769912"/>
-    <col min="9" max="9" width="12.7964601769912"/>
-    <col min="11" max="18" width="12.7964601769912"/>
-    <col min="20" max="20" width="12.7964601769912"/>
-    <col min="22" max="24" width="12.7964601769912"/>
-    <col min="26" max="26" width="12.7964601769912"/>
+    <col min="2" max="3" width="12.8"/>
+    <col min="5" max="6" width="12.8"/>
+    <col min="9" max="9" width="12.8"/>
+    <col min="11" max="18" width="12.8"/>
+    <col min="20" max="20" width="12.8"/>
+    <col min="22" max="24" width="12.8"/>
+    <col min="26" max="26" width="12.8"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:27">
+    <row r="1" s="1" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A1" s="3" t="s">
         <v>43</v>
       </c>
@@ -13948,7 +13948,7 @@
       <c r="Z1" s="4"/>
       <c r="AA1" s="5"/>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:27">
+    <row r="2" s="1" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -14031,7 +14031,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" customHeight="1" spans="1:27">
+    <row r="3" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A3" s="9" t="s">
         <v>133</v>
       </c>
@@ -14116,7 +14116,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" customHeight="1" spans="1:27">
+    <row r="4" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A4" s="13"/>
       <c r="B4" s="14">
         <v>2</v>
@@ -14199,7 +14199,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" customHeight="1" spans="1:27">
+    <row r="5" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A5" s="13"/>
       <c r="B5" s="14">
         <v>6</v>
@@ -14282,7 +14282,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:27">
+    <row r="6" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A6" s="13"/>
       <c r="B6" s="14">
         <v>7</v>
@@ -14365,7 +14365,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:27">
+    <row r="7" ht="13.5" customHeight="1" spans="1:27">
       <c r="A7" s="15"/>
       <c r="B7" s="14">
         <v>11</v>
@@ -14448,7 +14448,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:27">
+    <row r="8" ht="13.5" customHeight="1" spans="1:27">
       <c r="A8" s="15"/>
       <c r="B8" s="14">
         <v>12</v>
@@ -14531,7 +14531,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:27">
+    <row r="9" ht="13.5" customHeight="1" spans="1:27">
       <c r="A9" s="15"/>
       <c r="B9" s="14">
         <v>13</v>
@@ -14614,7 +14614,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:27">
+    <row r="10" ht="13.5" customHeight="1" spans="1:27">
       <c r="A10" s="15"/>
       <c r="B10" s="16">
         <v>8</v>
@@ -14697,7 +14697,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:27">
+    <row r="11" ht="13.5" customHeight="1" spans="1:27">
       <c r="A11" s="15"/>
       <c r="B11" s="16">
         <v>9</v>
@@ -14780,7 +14780,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:27">
+    <row r="12" ht="13.5" customHeight="1" spans="1:27">
       <c r="A12" s="15"/>
       <c r="B12" s="16">
         <v>10</v>
@@ -14863,7 +14863,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="13" customFormat="1" customHeight="1" spans="1:27">
+    <row r="13" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="C13">
         <f t="shared" ref="C13:AA13" si="2">AVERAGE(C3:C12)</f>
         <v>5</v>
@@ -14965,8 +14965,8 @@
         <v>70.3</v>
       </c>
     </row>
-    <row r="14" customHeight="1"/>
-    <row r="15" customHeight="1" spans="1:27">
+    <row r="14" ht="13.5" customHeight="1"/>
+    <row r="15" ht="13.5" customHeight="1" spans="1:27">
       <c r="A15" s="17" t="s">
         <v>134</v>
       </c>
@@ -15051,7 +15051,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:27">
+    <row r="16" ht="13.5" customHeight="1" spans="1:27">
       <c r="A16" s="17"/>
       <c r="B16" s="18">
         <v>2</v>
@@ -15134,7 +15134,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:27">
+    <row r="17" ht="13.5" customHeight="1" spans="1:27">
       <c r="A17" s="17"/>
       <c r="B17" s="18">
         <v>3</v>
@@ -15217,7 +15217,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="1:27">
+    <row r="18" ht="13.5" customHeight="1" spans="1:27">
       <c r="A18" s="17"/>
       <c r="B18" s="19">
         <v>4</v>
@@ -15300,7 +15300,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="1:27">
+    <row r="19" ht="13.5" customHeight="1" spans="1:27">
       <c r="A19" s="17"/>
       <c r="B19" s="19">
         <v>5</v>
@@ -15383,7 +15383,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="1:27">
+    <row r="20" ht="13.5" customHeight="1" spans="1:27">
       <c r="A20" s="17"/>
       <c r="B20" s="19">
         <v>6</v>
@@ -15466,7 +15466,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="1:27">
+    <row r="21" ht="13.5" customHeight="1" spans="1:27">
       <c r="A21" s="20"/>
       <c r="B21" s="21">
         <v>1</v>
@@ -15549,7 +15549,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" customFormat="1" customHeight="1" spans="1:27">
+    <row r="22" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A22" s="17"/>
       <c r="B22" s="22">
         <v>13</v>
@@ -15632,7 +15632,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="23" customFormat="1" customHeight="1" spans="1:27">
+    <row r="23" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A23" s="17"/>
       <c r="B23" s="22">
         <v>14</v>
@@ -15715,7 +15715,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="24" customFormat="1" customHeight="1" spans="1:27">
+    <row r="24" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A24" s="17"/>
       <c r="B24" s="22">
         <v>15</v>
@@ -15798,7 +15798,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" customFormat="1" customHeight="1" spans="1:27">
+    <row r="25" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A25" s="17"/>
       <c r="B25" s="22">
         <v>16</v>
@@ -15881,7 +15881,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26" customFormat="1" customHeight="1" spans="1:27">
+    <row r="26" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A26" s="17"/>
       <c r="B26" s="22">
         <v>17</v>
@@ -15964,7 +15964,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="27" customFormat="1" customHeight="1" spans="1:27">
+    <row r="27" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A27" s="17"/>
       <c r="B27" s="22">
         <v>18</v>
@@ -16047,7 +16047,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="28" customFormat="1" customHeight="1" spans="1:27">
+    <row r="28" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A28" s="17"/>
       <c r="B28" s="22">
         <v>19</v>
@@ -16130,7 +16130,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="29" customFormat="1" customHeight="1" spans="1:27">
+    <row r="29" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A29" s="17"/>
       <c r="B29" s="23">
         <v>9</v>
@@ -16213,7 +16213,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="30" customFormat="1" customHeight="1" spans="1:27">
+    <row r="30" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A30" s="17"/>
       <c r="B30" s="23">
         <v>10</v>
@@ -16296,7 +16296,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="31" customFormat="1" customHeight="1" spans="1:27">
+    <row r="31" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A31" s="17"/>
       <c r="B31" s="23">
         <v>11</v>
@@ -16379,7 +16379,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="1:27">
+    <row r="32" ht="13.5" customHeight="1" spans="1:27">
       <c r="C32">
         <f>AVERAGE(C15:C31)</f>
         <v>5</v>
@@ -16481,8 +16481,8 @@
         <v>70.9411764705882</v>
       </c>
     </row>
-    <row r="33" customHeight="1"/>
-    <row r="34" customHeight="1" spans="1:27">
+    <row r="33" ht="13.5" customHeight="1"/>
+    <row r="34" ht="13.5" customHeight="1" spans="1:27">
       <c r="A34" s="15" t="s">
         <v>135</v>
       </c>
@@ -16567,7 +16567,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="35" customHeight="1" spans="1:27">
+    <row r="35" ht="13.5" customHeight="1" spans="1:27">
       <c r="A35" s="15"/>
       <c r="B35" s="14">
         <v>4</v>
@@ -16650,7 +16650,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" customHeight="1" spans="1:27">
+    <row r="36" ht="13.5" customHeight="1" spans="1:27">
       <c r="A36" s="15"/>
       <c r="B36" s="14">
         <v>5</v>
@@ -16733,7 +16733,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="37" customHeight="1" spans="1:27">
+    <row r="37" ht="13.5" customHeight="1" spans="1:27">
       <c r="A37" s="15"/>
       <c r="B37" s="14">
         <v>8</v>
@@ -16816,7 +16816,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="38" customHeight="1" spans="1:27">
+    <row r="38" ht="13.5" customHeight="1" spans="1:27">
       <c r="A38" s="15"/>
       <c r="B38" s="14">
         <v>9</v>
@@ -16899,7 +16899,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="39" customHeight="1" spans="1:27">
+    <row r="39" ht="13.5" customHeight="1" spans="1:27">
       <c r="A39" s="15"/>
       <c r="B39" s="14">
         <v>10</v>
@@ -16982,7 +16982,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="40" customHeight="1" spans="1:27">
+    <row r="40" ht="13.5" customHeight="1" spans="1:27">
       <c r="A40" s="15"/>
       <c r="B40" s="14">
         <v>11</v>
@@ -17065,7 +17065,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="41" customHeight="1" spans="1:27">
+    <row r="41" ht="13.5" customHeight="1" spans="1:27">
       <c r="A41" s="15"/>
       <c r="B41" s="14">
         <v>12</v>
@@ -17148,7 +17148,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="42" customHeight="1" spans="1:27">
+    <row r="42" ht="13.5" customHeight="1" spans="1:27">
       <c r="A42" s="15"/>
       <c r="B42" s="14">
         <v>13</v>
@@ -17231,7 +17231,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="43" customHeight="1" spans="1:27">
+    <row r="43" ht="13.5" customHeight="1" spans="1:27">
       <c r="A43" s="15"/>
       <c r="B43" s="14">
         <v>14</v>
@@ -17314,7 +17314,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="44" customHeight="1" spans="1:27">
+    <row r="44" ht="13.5" customHeight="1" spans="1:27">
       <c r="A44" s="15"/>
       <c r="B44" s="14">
         <v>15</v>
@@ -17397,7 +17397,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="45" customHeight="1" spans="1:27">
+    <row r="45" ht="13.5" customHeight="1" spans="1:27">
       <c r="A45" s="15"/>
       <c r="B45" s="14">
         <v>16</v>
@@ -17480,7 +17480,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="46" customHeight="1" spans="1:27">
+    <row r="46" ht="13.5" customHeight="1" spans="1:27">
       <c r="A46" s="15"/>
       <c r="B46" s="14">
         <v>25</v>
@@ -17563,7 +17563,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="47" customHeight="1" spans="1:27">
+    <row r="47" ht="13.5" customHeight="1" spans="1:27">
       <c r="A47" s="15"/>
       <c r="B47" s="14">
         <v>39</v>
@@ -17646,7 +17646,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="48" customHeight="1" spans="1:27">
+    <row r="48" ht="13.5" customHeight="1" spans="1:27">
       <c r="A48" s="15"/>
       <c r="B48" s="14">
         <v>40</v>
@@ -17729,7 +17729,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="49" customHeight="1" spans="1:27">
+    <row r="49" ht="13.5" customHeight="1" spans="1:27">
       <c r="A49" s="15"/>
       <c r="B49" s="14">
         <v>41</v>
@@ -17812,7 +17812,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="50" customHeight="1" spans="1:27">
+    <row r="50" ht="13.5" customHeight="1" spans="1:27">
       <c r="A50" s="15"/>
       <c r="B50" s="14">
         <v>42</v>
@@ -17895,7 +17895,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="51" customHeight="1" spans="1:27">
+    <row r="51" ht="13.5" customHeight="1" spans="1:27">
       <c r="A51" s="15"/>
       <c r="B51" s="14">
         <v>43</v>
@@ -17978,7 +17978,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="52" customHeight="1" spans="1:27">
+    <row r="52" ht="13.5" customHeight="1" spans="1:27">
       <c r="A52" s="15"/>
       <c r="B52" s="16">
         <v>18</v>
@@ -18061,7 +18061,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="53" customHeight="1" spans="1:27">
+    <row r="53" ht="13.5" customHeight="1" spans="1:27">
       <c r="A53" s="15"/>
       <c r="B53" s="16">
         <v>19</v>
@@ -18144,7 +18144,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="54" customHeight="1" spans="1:27">
+    <row r="54" ht="13.5" customHeight="1" spans="1:27">
       <c r="A54" s="15"/>
       <c r="B54" s="16">
         <v>20</v>
@@ -18227,7 +18227,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="55" customHeight="1" spans="1:27">
+    <row r="55" ht="13.5" customHeight="1" spans="1:27">
       <c r="A55" s="15"/>
       <c r="B55" s="16">
         <v>21</v>
@@ -18310,7 +18310,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="56" customHeight="1" spans="1:27">
+    <row r="56" ht="13.5" customHeight="1" spans="1:27">
       <c r="A56" s="15"/>
       <c r="B56" s="16">
         <v>22</v>
@@ -18393,7 +18393,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="57" customHeight="1" spans="1:27">
+    <row r="57" ht="13.5" customHeight="1" spans="1:27">
       <c r="A57" s="15"/>
       <c r="B57" s="16">
         <v>23</v>
@@ -18476,7 +18476,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="58" customHeight="1" spans="1:27">
+    <row r="58" ht="13.5" customHeight="1" spans="1:27">
       <c r="A58" s="15"/>
       <c r="B58" s="16">
         <v>24</v>
@@ -18559,7 +18559,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="59" customHeight="1" spans="1:27">
+    <row r="59" ht="13.5" customHeight="1" spans="1:27">
       <c r="C59">
         <f>AVERAGE(C34:C58)</f>
         <v>4.92</v>
@@ -18661,8 +18661,8 @@
         <v>71.16</v>
       </c>
     </row>
-    <row r="60" customHeight="1"/>
-    <row r="61" customHeight="1" spans="1:27">
+    <row r="60" ht="13.5" customHeight="1"/>
+    <row r="61" ht="13.5" customHeight="1" spans="1:27">
       <c r="A61" s="24" t="s">
         <v>136</v>
       </c>
@@ -18747,7 +18747,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="62" customHeight="1" spans="1:27">
+    <row r="62" ht="13.5" customHeight="1" spans="1:27">
       <c r="A62" s="24"/>
       <c r="B62" s="25">
         <v>20</v>
@@ -18830,7 +18830,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="63" customHeight="1" spans="1:27">
+    <row r="63" ht="13.5" customHeight="1" spans="1:27">
       <c r="A63" s="24"/>
       <c r="B63" s="25">
         <v>21</v>
@@ -18913,7 +18913,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="64" customHeight="1" spans="1:27">
+    <row r="64" ht="13.5" customHeight="1" spans="1:27">
       <c r="A64" s="24"/>
       <c r="B64" s="25">
         <v>22</v>
@@ -18996,7 +18996,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="65" customHeight="1" spans="1:27">
+    <row r="65" ht="13.5" customHeight="1" spans="1:27">
       <c r="A65" s="24"/>
       <c r="B65" s="25">
         <v>23</v>
@@ -19079,7 +19079,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="66" customHeight="1" spans="1:27">
+    <row r="66" ht="13.5" customHeight="1" spans="1:27">
       <c r="A66" s="24"/>
       <c r="B66" s="25">
         <v>24</v>
@@ -19162,7 +19162,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="67" customHeight="1" spans="1:27">
+    <row r="67" ht="13.5" customHeight="1" spans="1:27">
       <c r="A67" s="24"/>
       <c r="B67" s="25">
         <v>25</v>
@@ -19245,7 +19245,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="68" customHeight="1" spans="1:27">
+    <row r="68" ht="13.5" customHeight="1" spans="1:27">
       <c r="A68" s="24"/>
       <c r="B68" s="25">
         <v>26</v>
@@ -19328,7 +19328,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="69" customHeight="1" spans="1:27">
+    <row r="69" ht="13.5" customHeight="1" spans="1:27">
       <c r="A69" s="24"/>
       <c r="B69" s="25">
         <v>27</v>
@@ -19411,7 +19411,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="70" customHeight="1" spans="1:27">
+    <row r="70" ht="13.5" customHeight="1" spans="1:27">
       <c r="A70" s="24"/>
       <c r="B70" s="25">
         <v>28</v>
@@ -19494,7 +19494,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="71" customHeight="1" spans="1:27">
+    <row r="71" ht="13.5" customHeight="1" spans="1:27">
       <c r="A71" s="24"/>
       <c r="B71" s="25">
         <v>29</v>
@@ -19577,7 +19577,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="72" customHeight="1" spans="1:27">
+    <row r="72" ht="13.5" customHeight="1" spans="1:27">
       <c r="A72" s="24"/>
       <c r="B72" s="25">
         <v>30</v>
@@ -19660,7 +19660,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="73" customHeight="1" spans="1:27">
+    <row r="73" ht="13.5" customHeight="1" spans="1:27">
       <c r="A73" s="24"/>
       <c r="B73" s="25">
         <v>31</v>
@@ -19743,7 +19743,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="74" customHeight="1" spans="1:27">
+    <row r="74" ht="13.5" customHeight="1" spans="1:27">
       <c r="A74" s="24"/>
       <c r="B74" s="25">
         <v>32</v>
@@ -19826,7 +19826,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="75" customHeight="1" spans="1:27">
+    <row r="75" ht="13.5" customHeight="1" spans="1:27">
       <c r="A75" s="15"/>
       <c r="B75" s="16">
         <v>15</v>
@@ -19909,7 +19909,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="76" customHeight="1" spans="1:27">
+    <row r="76" ht="13.5" customHeight="1" spans="1:27">
       <c r="A76" s="15"/>
       <c r="B76" s="16">
         <v>16</v>
@@ -19992,7 +19992,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="77" customHeight="1" spans="1:27">
+    <row r="77" ht="13.5" customHeight="1" spans="1:27">
       <c r="A77" s="24"/>
       <c r="B77" s="16">
         <v>17</v>
@@ -20075,7 +20075,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="78" customHeight="1" spans="1:27">
+    <row r="78" ht="13.5" customHeight="1" spans="1:27">
       <c r="A78" s="24"/>
       <c r="B78" s="16">
         <v>18</v>
@@ -20158,7 +20158,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="79" customHeight="1" spans="1:27">
+    <row r="79" ht="13.5" customHeight="1" spans="1:27">
       <c r="C79">
         <f>AVERAGE(C61:C78)</f>
         <v>5</v>
@@ -20278,22 +20278,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AB62"/>
-  <sheetFormatPr defaultColWidth="9.64601769911504" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.64545454545454" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="4.52212389380531" style="31" customWidth="1"/>
-    <col min="2" max="8" width="6.52212389380531" customWidth="1"/>
-    <col min="9" max="9" width="10.5663716814159" customWidth="1"/>
-    <col min="10" max="10" width="12.7964601769912" style="34"/>
-    <col min="11" max="15" width="12.7964601769912"/>
-    <col min="17" max="19" width="12.7964601769912"/>
-    <col min="20" max="21" width="11.6637168141593"/>
-    <col min="22" max="24" width="12.7964601769912"/>
-    <col min="26" max="26" width="12.9380530973451" customWidth="1"/>
-    <col min="27" max="27" width="12.7964601769912" style="34"/>
-    <col min="28" max="28" width="19.4424778761062" customWidth="1"/>
+    <col min="1" max="1" width="4.51818181818182" style="31" customWidth="1"/>
+    <col min="2" max="8" width="6.51818181818182" customWidth="1"/>
+    <col min="9" max="9" width="10.5636363636364" customWidth="1"/>
+    <col min="10" max="10" width="12.8" style="34"/>
+    <col min="11" max="15" width="12.8"/>
+    <col min="17" max="19" width="12.8"/>
+    <col min="20" max="21" width="11.6636363636364"/>
+    <col min="22" max="24" width="12.8"/>
+    <col min="26" max="26" width="12.9363636363636" customWidth="1"/>
+    <col min="27" max="27" width="12.8" style="34"/>
+    <col min="28" max="28" width="19.4454545454545" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="1" s="1" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A1" s="3" t="s">
         <v>43</v>
       </c>
@@ -20325,7 +20325,7 @@
       <c r="AA1" s="5"/>
       <c r="AB1" s="4"/>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="2" s="1" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -20411,7 +20411,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:28">
+    <row r="3" ht="13.5" customHeight="1" spans="1:28">
       <c r="A3" s="15" t="s">
         <v>28</v>
       </c>
@@ -20499,7 +20499,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:28">
+    <row r="4" ht="13.5" customHeight="1" spans="1:28">
       <c r="A4" s="15"/>
       <c r="B4" s="16">
         <v>19</v>
@@ -20585,7 +20585,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:28">
+    <row r="5" ht="13.5" customHeight="1" spans="1:28">
       <c r="A5" s="15"/>
       <c r="B5" s="16">
         <v>20</v>
@@ -20671,7 +20671,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:28">
+    <row r="6" ht="13.5" customHeight="1" spans="1:28">
       <c r="A6" s="15" t="s">
         <v>31</v>
       </c>
@@ -20759,7 +20759,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:28">
+    <row r="7" ht="13.5" customHeight="1" spans="1:28">
       <c r="A7" s="15"/>
       <c r="B7" s="16">
         <v>45</v>
@@ -20845,7 +20845,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:28">
+    <row r="8" ht="13.5" customHeight="1" spans="1:28">
       <c r="A8" s="15"/>
       <c r="B8" s="16">
         <v>46</v>
@@ -20931,7 +20931,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:28">
+    <row r="9" ht="13.5" customHeight="1" spans="1:28">
       <c r="A9" s="15"/>
       <c r="B9" s="16">
         <v>47</v>
@@ -21017,7 +21017,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:28">
+    <row r="10" ht="13.5" customHeight="1" spans="1:28">
       <c r="A10" s="15"/>
       <c r="B10" s="16">
         <v>48</v>
@@ -21103,7 +21103,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:28">
+    <row r="11" ht="13.5" customHeight="1" spans="1:28">
       <c r="A11" s="15"/>
       <c r="B11" s="16">
         <v>49</v>
@@ -21189,7 +21189,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:28">
+    <row r="12" ht="13.5" customHeight="1" spans="1:28">
       <c r="A12" s="15"/>
       <c r="B12" s="16">
         <v>50</v>
@@ -21275,7 +21275,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:28">
+    <row r="13" ht="13.5" customHeight="1" spans="1:28">
       <c r="A13" s="15" t="s">
         <v>45</v>
       </c>
@@ -21363,7 +21363,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:28">
+    <row r="14" ht="13.5" customHeight="1" spans="1:28">
       <c r="A14" s="15"/>
       <c r="B14" s="16">
         <v>34</v>
@@ -21449,7 +21449,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:28">
+    <row r="15" ht="13.5" customHeight="1" spans="1:28">
       <c r="A15" s="24"/>
       <c r="B15" s="16">
         <v>35</v>
@@ -21535,7 +21535,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:28">
+    <row r="16" ht="13.5" customHeight="1" spans="1:28">
       <c r="A16" s="24"/>
       <c r="B16" s="16">
         <v>36</v>
@@ -21621,7 +21621,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:28">
+    <row r="17" ht="13.5" customHeight="1" spans="1:28">
       <c r="A17" s="15" t="s">
         <v>33</v>
       </c>
@@ -21709,7 +21709,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="1:28">
+    <row r="18" ht="13.5" customHeight="1" spans="1:28">
       <c r="A18" s="15"/>
       <c r="B18" s="16">
         <v>11</v>
@@ -21795,7 +21795,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="1:28">
+    <row r="19" ht="13.5" customHeight="1" spans="1:28">
       <c r="A19" s="15"/>
       <c r="B19" s="16">
         <v>12</v>
@@ -21881,7 +21881,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" customFormat="1" customHeight="1" spans="1:28">
+    <row r="20" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A20" s="31" t="s">
         <v>34</v>
       </c>
@@ -21969,7 +21969,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="1:28">
+    <row r="21" ht="13.5" customHeight="1" spans="1:28">
       <c r="A21" s="32"/>
       <c r="B21" s="23">
         <v>21</v>
@@ -22055,7 +22055,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" customFormat="1" customHeight="1" spans="1:28">
+    <row r="22" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A22" s="31"/>
       <c r="B22" s="23">
         <v>22</v>
@@ -22252,7 +22252,7 @@
       <c r="A24" s="31"/>
       <c r="B24" s="23"/>
       <c r="C24" s="12">
-        <f t="shared" ref="C24:Z24" si="3">_xlfn.STDEV.S(C3:C22)</f>
+        <f t="shared" ref="C24:AA24" si="3">_xlfn.STDEV.S(C3:C22)</f>
         <v>0.366347548532523</v>
       </c>
       <c r="D24" s="12">
@@ -22348,7 +22348,7 @@
         <v>0</v>
       </c>
       <c r="AA24" s="12">
-        <f>_xlfn.STDEV.S(AA3:AA22)</f>
+        <f t="shared" si="3"/>
         <v>1.03998987849326</v>
       </c>
       <c r="AB24" s="11" t="s">
@@ -23520,16 +23520,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AB92"/>
-  <sheetFormatPr defaultColWidth="9.64601769911504" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.64545454545454" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="4.52212389380531" style="31" customWidth="1"/>
-    <col min="2" max="8" width="6.52212389380531" customWidth="1"/>
-    <col min="9" max="9" width="10.5663716814159" customWidth="1"/>
-    <col min="10" max="10" width="12.7964601769912" style="34"/>
-    <col min="11" max="25" width="12.7964601769912"/>
-    <col min="26" max="26" width="12.9380530973451" customWidth="1"/>
-    <col min="27" max="27" width="12.7964601769912" style="34"/>
-    <col min="28" max="28" width="19.4424778761062" customWidth="1"/>
+    <col min="1" max="1" width="4.51818181818182" style="31" customWidth="1"/>
+    <col min="2" max="8" width="6.51818181818182" customWidth="1"/>
+    <col min="9" max="9" width="10.5636363636364" customWidth="1"/>
+    <col min="10" max="10" width="12.8" style="34"/>
+    <col min="11" max="25" width="12.8"/>
+    <col min="26" max="26" width="12.9363636363636" customWidth="1"/>
+    <col min="27" max="27" width="12.8" style="34"/>
+    <col min="28" max="28" width="19.4454545454545" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:28">
@@ -23738,7 +23738,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" customHeight="1" spans="1:28">
+    <row r="4" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A4" s="13"/>
       <c r="B4" s="14">
         <v>4</v>
@@ -23824,7 +23824,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" customHeight="1" spans="1:28">
+    <row r="5" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A5" s="13"/>
       <c r="B5" s="14">
         <v>5</v>
@@ -23910,7 +23910,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:28">
+    <row r="6" ht="13.5" customHeight="1" spans="1:28">
       <c r="A6" s="15"/>
       <c r="B6" s="14">
         <v>14</v>
@@ -23996,7 +23996,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:28">
+    <row r="7" ht="13.5" customHeight="1" spans="1:28">
       <c r="A7" s="15"/>
       <c r="B7" s="14">
         <v>15</v>
@@ -24082,7 +24082,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:28">
+    <row r="8" ht="13.5" customHeight="1" spans="1:28">
       <c r="A8" s="15"/>
       <c r="B8" s="14">
         <v>16</v>
@@ -24168,7 +24168,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:28">
+    <row r="9" ht="13.5" customHeight="1" spans="1:28">
       <c r="A9" s="15"/>
       <c r="B9" s="14">
         <v>17</v>
@@ -24254,7 +24254,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:28">
+    <row r="10" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A10" s="9" t="s">
         <v>31</v>
       </c>
@@ -24342,7 +24342,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:28">
+    <row r="11" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A11" s="13"/>
       <c r="B11" s="14">
         <v>2</v>
@@ -24428,7 +24428,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:28">
+    <row r="12" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A12" s="13"/>
       <c r="B12" s="14">
         <v>6</v>
@@ -24514,7 +24514,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:28">
+    <row r="13" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A13" s="13"/>
       <c r="B13" s="14">
         <v>7</v>
@@ -24600,7 +24600,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:28">
+    <row r="14" ht="13.5" customHeight="1" spans="1:28">
       <c r="A14" s="15"/>
       <c r="B14" s="14">
         <v>17</v>
@@ -24686,7 +24686,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:28">
+    <row r="15" ht="13.5" customHeight="1" spans="1:28">
       <c r="A15" s="15"/>
       <c r="B15" s="14">
         <v>26</v>
@@ -24772,7 +24772,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:28">
+    <row r="16" ht="13.5" customHeight="1" spans="1:28">
       <c r="A16" s="15"/>
       <c r="B16" s="14">
         <v>27</v>
@@ -24858,7 +24858,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:28">
+    <row r="17" ht="13.5" customHeight="1" spans="1:28">
       <c r="A17" s="15"/>
       <c r="B17" s="14">
         <v>28</v>
@@ -24944,7 +24944,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="1:28">
+    <row r="18" ht="13.5" customHeight="1" spans="1:28">
       <c r="A18" s="15"/>
       <c r="B18" s="14">
         <v>29</v>
@@ -25030,7 +25030,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="1:28">
+    <row r="19" ht="13.5" customHeight="1" spans="1:28">
       <c r="A19" s="15"/>
       <c r="B19" s="14">
         <v>30</v>
@@ -25116,7 +25116,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="1:28">
+    <row r="20" ht="13.5" customHeight="1" spans="1:28">
       <c r="A20" s="15"/>
       <c r="B20" s="14">
         <v>31</v>
@@ -25202,7 +25202,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="1:28">
+    <row r="21" ht="13.5" customHeight="1" spans="1:28">
       <c r="A21" s="15"/>
       <c r="B21" s="14">
         <v>32</v>
@@ -25288,7 +25288,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="1:28">
+    <row r="22" ht="13.5" customHeight="1" spans="1:28">
       <c r="A22" s="15"/>
       <c r="B22" s="14">
         <v>33</v>
@@ -25374,7 +25374,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="1:28">
+    <row r="23" ht="13.5" customHeight="1" spans="1:28">
       <c r="A23" s="15"/>
       <c r="B23" s="14">
         <v>34</v>
@@ -25460,7 +25460,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="1:28">
+    <row r="24" ht="13.5" customHeight="1" spans="1:28">
       <c r="A24" s="15"/>
       <c r="B24" s="14">
         <v>35</v>
@@ -25546,7 +25546,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="1:28">
+    <row r="25" ht="13.5" customHeight="1" spans="1:28">
       <c r="A25" s="15"/>
       <c r="B25" s="14">
         <v>36</v>
@@ -25632,7 +25632,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="1:28">
+    <row r="26" ht="13.5" customHeight="1" spans="1:28">
       <c r="A26" s="15"/>
       <c r="B26" s="14">
         <v>37</v>
@@ -25718,7 +25718,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="1:28">
+    <row r="27" ht="13.5" customHeight="1" spans="1:28">
       <c r="A27" s="15"/>
       <c r="B27" s="14">
         <v>38</v>
@@ -25804,7 +25804,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="1:28">
+    <row r="28" ht="13.5" customHeight="1" spans="1:28">
       <c r="A28" s="30" t="s">
         <v>32</v>
       </c>
@@ -25892,7 +25892,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="1:28">
+    <row r="29" ht="13.5" customHeight="1" spans="1:28">
       <c r="A29" s="15"/>
       <c r="B29" s="10">
         <v>2</v>
@@ -25978,7 +25978,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="1:28">
+    <row r="30" ht="13.5" customHeight="1" spans="1:28">
       <c r="A30" s="15"/>
       <c r="B30" s="10">
         <v>3</v>
@@ -26064,7 +26064,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="1:28">
+    <row r="31" ht="13.5" customHeight="1" spans="1:28">
       <c r="A31" s="15"/>
       <c r="B31" s="10">
         <v>4</v>
@@ -26150,7 +26150,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="1:28">
+    <row r="32" ht="13.5" customHeight="1" spans="1:28">
       <c r="A32" s="15"/>
       <c r="B32" s="10">
         <v>5</v>
@@ -26236,7 +26236,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" customHeight="1" spans="1:28">
+    <row r="33" ht="13.5" customHeight="1" spans="1:28">
       <c r="A33" s="15"/>
       <c r="B33" s="10">
         <v>6</v>
@@ -26322,7 +26322,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="34" customHeight="1" spans="1:28">
+    <row r="34" ht="13.5" customHeight="1" spans="1:28">
       <c r="A34" s="15"/>
       <c r="B34" s="10">
         <v>7</v>
@@ -26408,7 +26408,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="35" customHeight="1" spans="1:28">
+    <row r="35" ht="13.5" customHeight="1" spans="1:28">
       <c r="A35" s="15"/>
       <c r="B35" s="10">
         <v>8</v>
@@ -26494,7 +26494,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="36" customHeight="1" spans="1:28">
+    <row r="36" ht="13.5" customHeight="1" spans="1:28">
       <c r="A36" s="15"/>
       <c r="B36" s="10">
         <v>9</v>
@@ -26580,7 +26580,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="37" customHeight="1" spans="1:28">
+    <row r="37" ht="13.5" customHeight="1" spans="1:28">
       <c r="A37" s="15"/>
       <c r="B37" s="10">
         <v>10</v>
@@ -26666,7 +26666,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="38" customHeight="1" spans="1:28">
+    <row r="38" ht="13.5" customHeight="1" spans="1:28">
       <c r="A38" s="15"/>
       <c r="B38" s="10">
         <v>11</v>
@@ -26752,7 +26752,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="39" customHeight="1" spans="1:28">
+    <row r="39" ht="13.5" customHeight="1" spans="1:28">
       <c r="A39" s="15"/>
       <c r="B39" s="10">
         <v>12</v>
@@ -26838,7 +26838,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="40" customHeight="1" spans="1:28">
+    <row r="40" ht="13.5" customHeight="1" spans="1:28">
       <c r="A40" s="15"/>
       <c r="B40" s="10">
         <v>13</v>
@@ -26924,7 +26924,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="41" customHeight="1" spans="1:28">
+    <row r="41" ht="13.5" customHeight="1" spans="1:28">
       <c r="A41" s="15"/>
       <c r="B41" s="10">
         <v>14</v>
@@ -27010,7 +27010,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="42" customHeight="1" spans="1:28">
+    <row r="42" ht="13.5" customHeight="1" spans="1:28">
       <c r="A42" s="15" t="s">
         <v>33</v>
       </c>
@@ -27098,7 +27098,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="43" customHeight="1" spans="1:28">
+    <row r="43" ht="13.5" customHeight="1" spans="1:28">
       <c r="A43" s="15"/>
       <c r="B43" s="14">
         <v>8</v>
@@ -27184,7 +27184,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="44" customHeight="1" spans="1:28">
+    <row r="44" ht="13.5" customHeight="1" spans="1:28">
       <c r="A44" s="24"/>
       <c r="B44" s="14">
         <v>9</v>
@@ -27270,7 +27270,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="45" customHeight="1" spans="1:28">
+    <row r="45" ht="13.5" customHeight="1" spans="1:28">
       <c r="A45" s="20" t="s">
         <v>34</v>
       </c>
@@ -27358,7 +27358,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="46" customHeight="1" spans="1:28">
+    <row r="46" ht="13.5" customHeight="1" spans="1:28">
       <c r="A46" s="20"/>
       <c r="B46" s="21">
         <v>3</v>
@@ -27444,7 +27444,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="47" customHeight="1" spans="1:28">
+    <row r="47" ht="13.5" customHeight="1" spans="1:28">
       <c r="A47" s="20"/>
       <c r="B47" s="21">
         <v>4</v>
@@ -27530,7 +27530,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="48" customHeight="1" spans="1:28">
+    <row r="48" ht="13.5" customHeight="1" spans="1:28">
       <c r="A48" s="20"/>
       <c r="B48" s="21">
         <v>5</v>
@@ -27615,7 +27615,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="49" customHeight="1" spans="1:28">
+    <row r="49" ht="13.5" customHeight="1" spans="1:28">
       <c r="A49" s="20"/>
       <c r="B49" s="21">
         <v>6</v>
@@ -27701,7 +27701,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="50" customHeight="1" spans="1:28">
+    <row r="50" ht="13.5" customHeight="1" spans="1:28">
       <c r="A50" s="20"/>
       <c r="B50" s="21">
         <v>7</v>
@@ -27787,7 +27787,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="51" customHeight="1" spans="1:28">
+    <row r="51" ht="13.5" customHeight="1" spans="1:28">
       <c r="A51" s="20"/>
       <c r="B51" s="21">
         <v>8</v>
@@ -27873,7 +27873,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="52" customHeight="1" spans="1:28">
+    <row r="52" ht="13.5" customHeight="1" spans="1:28">
       <c r="A52" s="28"/>
       <c r="B52" s="22">
         <v>12</v>
@@ -27959,7 +27959,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="53" customFormat="1" customHeight="1" spans="1:28">
+    <row r="53" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A53" s="15" t="s">
         <v>28</v>
       </c>
@@ -28047,7 +28047,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="54" customFormat="1" customHeight="1" spans="1:28">
+    <row r="54" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A54" s="15"/>
       <c r="B54" s="16">
         <v>19</v>
@@ -28133,7 +28133,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="55" customFormat="1" customHeight="1" spans="1:28">
+    <row r="55" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A55" s="15"/>
       <c r="B55" s="16">
         <v>20</v>
@@ -28219,7 +28219,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="56" customFormat="1" customHeight="1" spans="1:28">
+    <row r="56" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A56" s="15" t="s">
         <v>31</v>
       </c>
@@ -28307,7 +28307,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="57" customFormat="1" customHeight="1" spans="1:28">
+    <row r="57" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A57" s="15"/>
       <c r="B57" s="16">
         <v>45</v>
@@ -28393,7 +28393,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="58" customFormat="1" customHeight="1" spans="1:28">
+    <row r="58" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A58" s="15"/>
       <c r="B58" s="16">
         <v>46</v>
@@ -28479,7 +28479,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="59" customFormat="1" customHeight="1" spans="1:28">
+    <row r="59" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A59" s="15"/>
       <c r="B59" s="16">
         <v>47</v>
@@ -28565,7 +28565,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="60" customFormat="1" customHeight="1" spans="1:28">
+    <row r="60" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A60" s="15"/>
       <c r="B60" s="16">
         <v>48</v>
@@ -28651,7 +28651,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="61" customFormat="1" customHeight="1" spans="1:28">
+    <row r="61" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A61" s="15"/>
       <c r="B61" s="16">
         <v>49</v>
@@ -28737,7 +28737,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="62" customFormat="1" customHeight="1" spans="1:28">
+    <row r="62" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A62" s="15"/>
       <c r="B62" s="16">
         <v>50</v>
@@ -28823,7 +28823,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="63" customFormat="1" customHeight="1" spans="1:28">
+    <row r="63" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A63" s="15" t="s">
         <v>45</v>
       </c>
@@ -28911,7 +28911,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="64" customFormat="1" customHeight="1" spans="1:28">
+    <row r="64" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A64" s="15"/>
       <c r="B64" s="16">
         <v>34</v>
@@ -28997,7 +28997,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="65" customFormat="1" customHeight="1" spans="1:28">
+    <row r="65" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A65" s="24"/>
       <c r="B65" s="16">
         <v>35</v>
@@ -29083,7 +29083,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="66" customFormat="1" customHeight="1" spans="1:28">
+    <row r="66" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A66" s="24"/>
       <c r="B66" s="16">
         <v>36</v>
@@ -29169,7 +29169,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="67" customFormat="1" customHeight="1" spans="1:28">
+    <row r="67" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A67" s="15" t="s">
         <v>33</v>
       </c>
@@ -29257,7 +29257,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="68" customFormat="1" customHeight="1" spans="1:28">
+    <row r="68" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A68" s="15"/>
       <c r="B68" s="16">
         <v>11</v>
@@ -29343,7 +29343,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="69" customFormat="1" customHeight="1" spans="1:28">
+    <row r="69" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A69" s="15"/>
       <c r="B69" s="16">
         <v>12</v>
@@ -29429,7 +29429,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="70" customFormat="1" customHeight="1" spans="1:28">
+    <row r="70" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A70" s="31" t="s">
         <v>34</v>
       </c>
@@ -29517,7 +29517,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="71" customFormat="1" customHeight="1" spans="1:28">
+    <row r="71" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A71" s="32"/>
       <c r="B71" s="23">
         <v>21</v>
@@ -29603,7 +29603,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="72" customFormat="1" customHeight="1" spans="1:28">
+    <row r="72" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A72" s="31"/>
       <c r="B72" s="23">
         <v>22</v>
@@ -30477,23 +30477,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AB92"/>
-  <sheetFormatPr defaultColWidth="9.64601769911504" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.64545454545454" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="4.52212389380531" style="31" customWidth="1"/>
-    <col min="2" max="8" width="6.52212389380531" customWidth="1"/>
-    <col min="9" max="9" width="10.5663716814159" customWidth="1"/>
-    <col min="10" max="10" width="12.7964601769912" style="34"/>
-    <col min="11" max="11" width="12.7964601769912"/>
-    <col min="12" max="12" width="11.6637168141593"/>
-    <col min="13" max="18" width="12.7964601769912"/>
-    <col min="20" max="23" width="12.7964601769912"/>
-    <col min="24" max="24" width="11.6637168141593"/>
-    <col min="26" max="26" width="12.9380530973451" customWidth="1"/>
-    <col min="27" max="27" width="12.7964601769912" style="34"/>
-    <col min="28" max="28" width="19.4424778761062" customWidth="1"/>
+    <col min="1" max="1" width="4.51818181818182" style="31" customWidth="1"/>
+    <col min="2" max="8" width="6.51818181818182" customWidth="1"/>
+    <col min="9" max="9" width="10.5636363636364" customWidth="1"/>
+    <col min="10" max="10" width="12.8" style="34"/>
+    <col min="11" max="11" width="12.8"/>
+    <col min="12" max="12" width="11.6636363636364"/>
+    <col min="13" max="18" width="12.8"/>
+    <col min="20" max="23" width="12.8"/>
+    <col min="24" max="24" width="11.6636363636364"/>
+    <col min="26" max="26" width="12.9363636363636" customWidth="1"/>
+    <col min="27" max="27" width="12.8" style="34"/>
+    <col min="28" max="28" width="19.4454545454545" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="1" s="1" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A1" s="3" t="s">
         <v>43</v>
       </c>
@@ -30525,7 +30525,7 @@
       <c r="AA1" s="5"/>
       <c r="AB1" s="4"/>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="2" s="1" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -30611,7 +30611,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" customHeight="1" spans="1:28">
+    <row r="3" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A3" s="9" t="s">
         <v>28</v>
       </c>
@@ -30699,7 +30699,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" customHeight="1" spans="1:28">
+    <row r="4" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A4" s="13"/>
       <c r="B4" s="14">
         <v>2</v>
@@ -30785,7 +30785,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" customHeight="1" spans="1:28">
+    <row r="5" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A5" s="13"/>
       <c r="B5" s="14">
         <v>6</v>
@@ -30871,7 +30871,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:28">
+    <row r="6" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A6" s="13"/>
       <c r="B6" s="14">
         <v>7</v>
@@ -30957,7 +30957,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:28">
+    <row r="7" ht="13.5" customHeight="1" spans="1:28">
       <c r="A7" s="15"/>
       <c r="B7" s="14">
         <v>11</v>
@@ -31043,7 +31043,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:28">
+    <row r="8" ht="13.5" customHeight="1" spans="1:28">
       <c r="A8" s="15"/>
       <c r="B8" s="14">
         <v>12</v>
@@ -31129,7 +31129,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:28">
+    <row r="9" ht="13.5" customHeight="1" spans="1:28">
       <c r="A9" s="15"/>
       <c r="B9" s="14">
         <v>13</v>
@@ -31215,7 +31215,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:28">
+    <row r="10" ht="13.5" customHeight="1" spans="1:28">
       <c r="A10" s="15" t="s">
         <v>31</v>
       </c>
@@ -31303,7 +31303,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:28">
+    <row r="11" ht="13.5" customHeight="1" spans="1:28">
       <c r="A11" s="15"/>
       <c r="B11" s="14">
         <v>4</v>
@@ -31389,7 +31389,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:28">
+    <row r="12" ht="13.5" customHeight="1" spans="1:28">
       <c r="A12" s="15"/>
       <c r="B12" s="14">
         <v>5</v>
@@ -31475,7 +31475,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:28">
+    <row r="13" ht="13.5" customHeight="1" spans="1:28">
       <c r="A13" s="15"/>
       <c r="B13" s="14">
         <v>8</v>
@@ -31561,7 +31561,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:28">
+    <row r="14" ht="13.5" customHeight="1" spans="1:28">
       <c r="A14" s="15"/>
       <c r="B14" s="14">
         <v>9</v>
@@ -31647,7 +31647,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:28">
+    <row r="15" ht="13.5" customHeight="1" spans="1:28">
       <c r="A15" s="15"/>
       <c r="B15" s="14">
         <v>10</v>
@@ -31733,7 +31733,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:28">
+    <row r="16" ht="13.5" customHeight="1" spans="1:28">
       <c r="A16" s="15"/>
       <c r="B16" s="14">
         <v>11</v>
@@ -31819,7 +31819,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:28">
+    <row r="17" ht="13.5" customHeight="1" spans="1:28">
       <c r="A17" s="15"/>
       <c r="B17" s="14">
         <v>12</v>
@@ -31905,7 +31905,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="1:28">
+    <row r="18" ht="13.5" customHeight="1" spans="1:28">
       <c r="A18" s="15"/>
       <c r="B18" s="14">
         <v>13</v>
@@ -31991,7 +31991,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="1:28">
+    <row r="19" ht="13.5" customHeight="1" spans="1:28">
       <c r="A19" s="15"/>
       <c r="B19" s="14">
         <v>14</v>
@@ -32077,7 +32077,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="1:28">
+    <row r="20" ht="13.5" customHeight="1" spans="1:28">
       <c r="A20" s="15"/>
       <c r="B20" s="14">
         <v>15</v>
@@ -32163,7 +32163,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="1:28">
+    <row r="21" ht="13.5" customHeight="1" spans="1:28">
       <c r="A21" s="15"/>
       <c r="B21" s="14">
         <v>16</v>
@@ -32249,7 +32249,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="1:28">
+    <row r="22" ht="13.5" customHeight="1" spans="1:28">
       <c r="A22" s="15"/>
       <c r="B22" s="14">
         <v>25</v>
@@ -32335,7 +32335,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="1:28">
+    <row r="23" ht="13.5" customHeight="1" spans="1:28">
       <c r="A23" s="15"/>
       <c r="B23" s="14">
         <v>39</v>
@@ -32421,7 +32421,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="1:28">
+    <row r="24" ht="13.5" customHeight="1" spans="1:28">
       <c r="A24" s="15"/>
       <c r="B24" s="14">
         <v>40</v>
@@ -32507,7 +32507,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="1:28">
+    <row r="25" ht="13.5" customHeight="1" spans="1:28">
       <c r="A25" s="15"/>
       <c r="B25" s="14">
         <v>41</v>
@@ -32593,7 +32593,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="1:28">
+    <row r="26" ht="13.5" customHeight="1" spans="1:28">
       <c r="A26" s="15"/>
       <c r="B26" s="14">
         <v>42</v>
@@ -32679,7 +32679,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="1:28">
+    <row r="27" ht="13.5" customHeight="1" spans="1:28">
       <c r="A27" s="15"/>
       <c r="B27" s="14">
         <v>43</v>
@@ -32765,7 +32765,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="1:28">
+    <row r="28" ht="13.5" customHeight="1" spans="1:28">
       <c r="A28" s="24" t="s">
         <v>45</v>
       </c>
@@ -32853,7 +32853,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="1:28">
+    <row r="29" ht="13.5" customHeight="1" spans="1:28">
       <c r="A29" s="24"/>
       <c r="B29" s="25">
         <v>20</v>
@@ -32939,7 +32939,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="1:28">
+    <row r="30" ht="13.5" customHeight="1" spans="1:28">
       <c r="A30" s="24"/>
       <c r="B30" s="25">
         <v>21</v>
@@ -33025,7 +33025,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="1:28">
+    <row r="31" ht="13.5" customHeight="1" spans="1:28">
       <c r="A31" s="24"/>
       <c r="B31" s="25">
         <v>22</v>
@@ -33111,7 +33111,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="1:28">
+    <row r="32" ht="13.5" customHeight="1" spans="1:28">
       <c r="A32" s="24"/>
       <c r="B32" s="25">
         <v>23</v>
@@ -33197,7 +33197,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" customHeight="1" spans="1:28">
+    <row r="33" ht="13.5" customHeight="1" spans="1:28">
       <c r="A33" s="24"/>
       <c r="B33" s="25">
         <v>24</v>
@@ -33283,7 +33283,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="34" customHeight="1" spans="1:28">
+    <row r="34" ht="13.5" customHeight="1" spans="1:28">
       <c r="A34" s="24"/>
       <c r="B34" s="25">
         <v>25</v>
@@ -33369,7 +33369,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="35" customHeight="1" spans="1:28">
+    <row r="35" ht="13.5" customHeight="1" spans="1:28">
       <c r="A35" s="24"/>
       <c r="B35" s="25">
         <v>26</v>
@@ -33455,7 +33455,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="36" customHeight="1" spans="1:28">
+    <row r="36" ht="13.5" customHeight="1" spans="1:28">
       <c r="A36" s="24"/>
       <c r="B36" s="25">
         <v>27</v>
@@ -33541,7 +33541,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="37" customHeight="1" spans="1:28">
+    <row r="37" ht="13.5" customHeight="1" spans="1:28">
       <c r="A37" s="24"/>
       <c r="B37" s="25">
         <v>28</v>
@@ -33627,7 +33627,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="38" customHeight="1" spans="1:28">
+    <row r="38" ht="13.5" customHeight="1" spans="1:28">
       <c r="A38" s="24"/>
       <c r="B38" s="25">
         <v>29</v>
@@ -33713,7 +33713,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="39" customHeight="1" spans="1:28">
+    <row r="39" ht="13.5" customHeight="1" spans="1:28">
       <c r="A39" s="24"/>
       <c r="B39" s="25">
         <v>30</v>
@@ -33799,7 +33799,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="40" customHeight="1" spans="1:28">
+    <row r="40" ht="13.5" customHeight="1" spans="1:28">
       <c r="A40" s="24"/>
       <c r="B40" s="25">
         <v>31</v>
@@ -33885,7 +33885,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="41" customHeight="1" spans="1:28">
+    <row r="41" ht="13.5" customHeight="1" spans="1:28">
       <c r="A41" s="24"/>
       <c r="B41" s="25">
         <v>32</v>
@@ -33971,7 +33971,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="42" customHeight="1" spans="1:28">
+    <row r="42" ht="13.5" customHeight="1" spans="1:28">
       <c r="A42" s="15" t="s">
         <v>33</v>
       </c>
@@ -34059,7 +34059,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="43" customHeight="1" spans="1:28">
+    <row r="43" ht="13.5" customHeight="1" spans="1:28">
       <c r="A43" s="15"/>
       <c r="B43" s="14">
         <v>2</v>
@@ -34145,7 +34145,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="44" customHeight="1" spans="1:28">
+    <row r="44" ht="13.5" customHeight="1" spans="1:28">
       <c r="A44" s="15"/>
       <c r="B44" s="14">
         <v>3</v>
@@ -34231,7 +34231,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="45" customHeight="1" spans="1:28">
+    <row r="45" ht="13.5" customHeight="1" spans="1:28">
       <c r="A45" s="20" t="s">
         <v>59</v>
       </c>
@@ -34319,7 +34319,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="46" customFormat="1" customHeight="1" spans="1:28">
+    <row r="46" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A46" s="28"/>
       <c r="B46" s="22">
         <v>13</v>
@@ -34405,7 +34405,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="47" customFormat="1" customHeight="1" spans="1:28">
+    <row r="47" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A47" s="28"/>
       <c r="B47" s="22">
         <v>14</v>
@@ -34491,7 +34491,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="48" customFormat="1" customHeight="1" spans="1:28">
+    <row r="48" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A48" s="28"/>
       <c r="B48" s="22">
         <v>15</v>
@@ -34577,7 +34577,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="49" customFormat="1" customHeight="1" spans="1:28">
+    <row r="49" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A49" s="28"/>
       <c r="B49" s="22">
         <v>16</v>
@@ -34663,7 +34663,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="50" customFormat="1" customHeight="1" spans="1:28">
+    <row r="50" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A50" s="28"/>
       <c r="B50" s="22">
         <v>17</v>
@@ -34749,7 +34749,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="51" customFormat="1" customHeight="1" spans="1:28">
+    <row r="51" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A51" s="28"/>
       <c r="B51" s="22">
         <v>18</v>
@@ -34835,7 +34835,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="52" customFormat="1" customHeight="1" spans="1:28">
+    <row r="52" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A52" s="28"/>
       <c r="B52" s="22">
         <v>19</v>
@@ -34921,7 +34921,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="53" customFormat="1" customHeight="1" spans="1:28">
+    <row r="53" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A53" s="31"/>
       <c r="B53" s="23" t="s">
         <v>35</v>
@@ -35030,13 +35030,13 @@
         <v>60</v>
       </c>
     </row>
-    <row r="54" customFormat="1" customHeight="1" spans="1:28">
+    <row r="54" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A54" s="31"/>
       <c r="B54" s="23" t="s">
         <v>37</v>
       </c>
       <c r="C54" s="12">
-        <f t="shared" ref="C54:Z54" si="3">_xlfn.STDEV.S(C3:C52)</f>
+        <f t="shared" ref="C54:AA54" si="3">_xlfn.STDEV.S(C3:C52)</f>
         <v>0.197948663722157</v>
       </c>
       <c r="D54" s="12">
@@ -35132,7 +35132,7 @@
         <v>0.282842712474619</v>
       </c>
       <c r="AA54" s="12">
-        <f>_xlfn.STDEV.S(AA3:AA52)</f>
+        <f t="shared" si="3"/>
         <v>1.26958132259965</v>
       </c>
       <c r="AB54" s="11" t="s">
@@ -36304,17 +36304,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AB62"/>
-  <sheetFormatPr defaultColWidth="9.64601769911504" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.64545454545454" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="4.52212389380531" style="31" customWidth="1"/>
-    <col min="2" max="8" width="6.52212389380531" customWidth="1"/>
-    <col min="9" max="9" width="10.5663716814159" customWidth="1"/>
-    <col min="10" max="10" width="12.7964601769912" style="34"/>
-    <col min="15" max="15" width="12.7964601769912"/>
-    <col min="23" max="24" width="12.7964601769912"/>
-    <col min="26" max="26" width="12.9380530973451" customWidth="1"/>
-    <col min="27" max="27" width="12.7964601769912" style="34"/>
-    <col min="28" max="28" width="19.4424778761062" customWidth="1"/>
+    <col min="1" max="1" width="4.51818181818182" style="31" customWidth="1"/>
+    <col min="2" max="8" width="6.51818181818182" customWidth="1"/>
+    <col min="9" max="9" width="10.5636363636364" customWidth="1"/>
+    <col min="10" max="10" width="12.8" style="34"/>
+    <col min="15" max="15" width="12.8"/>
+    <col min="23" max="24" width="12.8"/>
+    <col min="26" max="26" width="12.9363636363636" customWidth="1"/>
+    <col min="27" max="27" width="12.8" style="34"/>
+    <col min="28" max="28" width="19.4454545454545" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:28">
@@ -36349,7 +36349,7 @@
       <c r="AA1" s="5"/>
       <c r="AB1" s="4"/>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="2" s="1" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -36435,7 +36435,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:28">
+    <row r="3" ht="13.5" customHeight="1" spans="1:28">
       <c r="A3" s="15" t="s">
         <v>28</v>
       </c>
@@ -36523,7 +36523,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:28">
+    <row r="4" ht="13.5" customHeight="1" spans="1:28">
       <c r="A4" s="15"/>
       <c r="B4" s="16">
         <v>9</v>
@@ -36609,7 +36609,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:28">
+    <row r="5" ht="13.5" customHeight="1" spans="1:28">
       <c r="A5" s="15"/>
       <c r="B5" s="16">
         <v>10</v>
@@ -36695,7 +36695,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:28">
+    <row r="6" ht="13.5" customHeight="1" spans="1:28">
       <c r="A6" s="15" t="s">
         <v>31</v>
       </c>
@@ -36783,7 +36783,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:28">
+    <row r="7" ht="13.5" customHeight="1" spans="1:28">
       <c r="A7" s="15"/>
       <c r="B7" s="16">
         <v>19</v>
@@ -36869,7 +36869,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:28">
+    <row r="8" ht="13.5" customHeight="1" spans="1:28">
       <c r="A8" s="15"/>
       <c r="B8" s="16">
         <v>20</v>
@@ -36955,7 +36955,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:28">
+    <row r="9" ht="13.5" customHeight="1" spans="1:28">
       <c r="A9" s="15"/>
       <c r="B9" s="16">
         <v>21</v>
@@ -37041,7 +37041,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:28">
+    <row r="10" ht="13.5" customHeight="1" spans="1:28">
       <c r="A10" s="15"/>
       <c r="B10" s="16">
         <v>22</v>
@@ -37127,7 +37127,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:28">
+    <row r="11" ht="13.5" customHeight="1" spans="1:28">
       <c r="A11" s="15"/>
       <c r="B11" s="16">
         <v>23</v>
@@ -37213,7 +37213,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:28">
+    <row r="12" ht="13.5" customHeight="1" spans="1:28">
       <c r="A12" s="15"/>
       <c r="B12" s="16">
         <v>24</v>
@@ -37299,7 +37299,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:28">
+    <row r="13" ht="13.5" customHeight="1" spans="1:28">
       <c r="A13" s="15" t="s">
         <v>45</v>
       </c>
@@ -37387,7 +37387,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:28">
+    <row r="14" ht="13.5" customHeight="1" spans="1:28">
       <c r="A14" s="15"/>
       <c r="B14" s="16">
         <v>16</v>
@@ -37473,7 +37473,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:28">
+    <row r="15" ht="13.5" customHeight="1" spans="1:28">
       <c r="A15" s="24"/>
       <c r="B15" s="16">
         <v>17</v>
@@ -37559,7 +37559,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:28">
+    <row r="16" ht="13.5" customHeight="1" spans="1:28">
       <c r="A16" s="24"/>
       <c r="B16" s="16">
         <v>18</v>
@@ -37645,7 +37645,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:28">
+    <row r="17" ht="13.5" customHeight="1" spans="1:28">
       <c r="A17" s="15" t="s">
         <v>33</v>
       </c>
@@ -37733,7 +37733,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="1:28">
+    <row r="18" ht="13.5" customHeight="1" spans="1:28">
       <c r="A18" s="15"/>
       <c r="B18" s="16">
         <v>5</v>
@@ -37819,7 +37819,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="1:28">
+    <row r="19" ht="13.5" customHeight="1" spans="1:28">
       <c r="A19" s="15"/>
       <c r="B19" s="16">
         <v>6</v>
@@ -37905,7 +37905,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" customFormat="1" customHeight="1" spans="1:28">
+    <row r="20" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A20" s="31" t="s">
         <v>34</v>
       </c>
@@ -37993,7 +37993,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="1:28">
+    <row r="21" ht="13.5" customHeight="1" spans="1:28">
       <c r="B21" s="23">
         <v>10</v>
       </c>
@@ -38078,7 +38078,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" customFormat="1" customHeight="1" spans="1:28">
+    <row r="22" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A22" s="31"/>
       <c r="B22" s="23">
         <v>11</v>
@@ -38164,7 +38164,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" customFormat="1" customHeight="1" spans="1:28">
+    <row r="23" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A23" s="31"/>
       <c r="B23" s="23" t="s">
         <v>35</v>
@@ -38279,7 +38279,7 @@
         <v>37</v>
       </c>
       <c r="C24" s="12">
-        <f t="shared" ref="C24:Z24" si="3">_xlfn.STDEV.S(C3:C22)</f>
+        <f t="shared" ref="C24:AA24" si="3">_xlfn.STDEV.S(C3:C22)</f>
         <v>0</v>
       </c>
       <c r="D24" s="12">
@@ -38375,7 +38375,7 @@
         <v>0</v>
       </c>
       <c r="AA24" s="12">
-        <f>_xlfn.STDEV.S(AA3:AA22)</f>
+        <f t="shared" si="3"/>
         <v>1.27630222456166</v>
       </c>
       <c r="AB24" s="11" t="s">
@@ -39548,22 +39548,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AB92"/>
-  <sheetFormatPr defaultColWidth="9.64601769911504" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.64545454545454" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="4.52212389380531" style="31" customWidth="1"/>
-    <col min="2" max="8" width="6.52212389380531" customWidth="1"/>
-    <col min="9" max="9" width="10.5663716814159" customWidth="1"/>
-    <col min="10" max="10" width="12.7964601769912" style="34"/>
-    <col min="11" max="11" width="12.7964601769912"/>
-    <col min="12" max="12" width="11.6637168141593"/>
-    <col min="13" max="18" width="12.7964601769912"/>
-    <col min="20" max="24" width="12.7964601769912"/>
-    <col min="26" max="26" width="12.9380530973451" customWidth="1"/>
-    <col min="27" max="27" width="12.7964601769912" style="34"/>
-    <col min="28" max="28" width="19.4424778761062" customWidth="1"/>
+    <col min="1" max="1" width="4.51818181818182" style="31" customWidth="1"/>
+    <col min="2" max="8" width="6.51818181818182" customWidth="1"/>
+    <col min="9" max="9" width="10.5636363636364" customWidth="1"/>
+    <col min="10" max="10" width="12.8" style="34"/>
+    <col min="11" max="11" width="12.8"/>
+    <col min="12" max="12" width="11.6636363636364"/>
+    <col min="13" max="18" width="12.8"/>
+    <col min="20" max="24" width="12.8"/>
+    <col min="26" max="26" width="12.9363636363636" customWidth="1"/>
+    <col min="27" max="27" width="12.8" style="34"/>
+    <col min="28" max="28" width="19.4454545454545" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="1" s="1" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A1" s="3" t="s">
         <v>43</v>
       </c>
@@ -39595,7 +39595,7 @@
       <c r="AA1" s="5"/>
       <c r="AB1" s="4"/>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="2" s="1" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -39681,7 +39681,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" customHeight="1" spans="1:28">
+    <row r="3" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A3" s="9" t="s">
         <v>28</v>
       </c>
@@ -39769,7 +39769,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" customHeight="1" spans="1:28">
+    <row r="4" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A4" s="13"/>
       <c r="B4" s="14">
         <v>2</v>
@@ -39855,7 +39855,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" customHeight="1" spans="1:28">
+    <row r="5" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A5" s="13"/>
       <c r="B5" s="14">
         <v>6</v>
@@ -39941,7 +39941,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:28">
+    <row r="6" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A6" s="13"/>
       <c r="B6" s="14">
         <v>7</v>
@@ -40027,7 +40027,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:28">
+    <row r="7" ht="13.5" customHeight="1" spans="1:28">
       <c r="A7" s="15"/>
       <c r="B7" s="14">
         <v>11</v>
@@ -40113,7 +40113,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:28">
+    <row r="8" ht="13.5" customHeight="1" spans="1:28">
       <c r="A8" s="15"/>
       <c r="B8" s="14">
         <v>12</v>
@@ -40199,7 +40199,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:28">
+    <row r="9" ht="13.5" customHeight="1" spans="1:28">
       <c r="A9" s="15"/>
       <c r="B9" s="14">
         <v>13</v>
@@ -40285,7 +40285,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:28">
+    <row r="10" ht="13.5" customHeight="1" spans="1:28">
       <c r="A10" s="15" t="s">
         <v>31</v>
       </c>
@@ -40373,7 +40373,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:28">
+    <row r="11" ht="13.5" customHeight="1" spans="1:28">
       <c r="A11" s="15"/>
       <c r="B11" s="14">
         <v>4</v>
@@ -40459,7 +40459,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:28">
+    <row r="12" ht="13.5" customHeight="1" spans="1:28">
       <c r="A12" s="15"/>
       <c r="B12" s="14">
         <v>5</v>
@@ -40545,7 +40545,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:28">
+    <row r="13" ht="13.5" customHeight="1" spans="1:28">
       <c r="A13" s="15"/>
       <c r="B13" s="14">
         <v>8</v>
@@ -40631,7 +40631,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:28">
+    <row r="14" ht="13.5" customHeight="1" spans="1:28">
       <c r="A14" s="15"/>
       <c r="B14" s="14">
         <v>9</v>
@@ -40717,7 +40717,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:28">
+    <row r="15" ht="13.5" customHeight="1" spans="1:28">
       <c r="A15" s="15"/>
       <c r="B15" s="14">
         <v>10</v>
@@ -40803,7 +40803,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:28">
+    <row r="16" ht="13.5" customHeight="1" spans="1:28">
       <c r="A16" s="15"/>
       <c r="B16" s="14">
         <v>11</v>
@@ -40889,7 +40889,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:28">
+    <row r="17" ht="13.5" customHeight="1" spans="1:28">
       <c r="A17" s="15"/>
       <c r="B17" s="14">
         <v>12</v>
@@ -40975,7 +40975,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="1:28">
+    <row r="18" ht="13.5" customHeight="1" spans="1:28">
       <c r="A18" s="15"/>
       <c r="B18" s="14">
         <v>13</v>
@@ -41061,7 +41061,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="1:28">
+    <row r="19" ht="13.5" customHeight="1" spans="1:28">
       <c r="A19" s="15"/>
       <c r="B19" s="14">
         <v>14</v>
@@ -41147,7 +41147,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="1:28">
+    <row r="20" ht="13.5" customHeight="1" spans="1:28">
       <c r="A20" s="15"/>
       <c r="B20" s="14">
         <v>15</v>
@@ -41233,7 +41233,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="1:28">
+    <row r="21" ht="13.5" customHeight="1" spans="1:28">
       <c r="A21" s="15"/>
       <c r="B21" s="14">
         <v>16</v>
@@ -41319,7 +41319,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="1:28">
+    <row r="22" ht="13.5" customHeight="1" spans="1:28">
       <c r="A22" s="15"/>
       <c r="B22" s="14">
         <v>25</v>
@@ -41405,7 +41405,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="1:28">
+    <row r="23" ht="13.5" customHeight="1" spans="1:28">
       <c r="A23" s="15"/>
       <c r="B23" s="14">
         <v>39</v>
@@ -41491,7 +41491,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="1:28">
+    <row r="24" ht="13.5" customHeight="1" spans="1:28">
       <c r="A24" s="15"/>
       <c r="B24" s="14">
         <v>40</v>
@@ -41577,7 +41577,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="1:28">
+    <row r="25" ht="13.5" customHeight="1" spans="1:28">
       <c r="A25" s="15"/>
       <c r="B25" s="14">
         <v>41</v>
@@ -41663,7 +41663,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="1:28">
+    <row r="26" ht="13.5" customHeight="1" spans="1:28">
       <c r="A26" s="15"/>
       <c r="B26" s="14">
         <v>42</v>
@@ -41749,7 +41749,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="1:28">
+    <row r="27" ht="13.5" customHeight="1" spans="1:28">
       <c r="A27" s="15"/>
       <c r="B27" s="14">
         <v>43</v>
@@ -41835,7 +41835,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="1:28">
+    <row r="28" ht="13.5" customHeight="1" spans="1:28">
       <c r="A28" s="24" t="s">
         <v>45</v>
       </c>
@@ -41923,7 +41923,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="1:28">
+    <row r="29" ht="13.5" customHeight="1" spans="1:28">
       <c r="A29" s="24"/>
       <c r="B29" s="25">
         <v>20</v>
@@ -42009,7 +42009,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="1:28">
+    <row r="30" ht="13.5" customHeight="1" spans="1:28">
       <c r="A30" s="24"/>
       <c r="B30" s="25">
         <v>21</v>
@@ -42095,7 +42095,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="1:28">
+    <row r="31" ht="13.5" customHeight="1" spans="1:28">
       <c r="A31" s="24"/>
       <c r="B31" s="25">
         <v>22</v>
@@ -42181,7 +42181,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="1:28">
+    <row r="32" ht="13.5" customHeight="1" spans="1:28">
       <c r="A32" s="24"/>
       <c r="B32" s="25">
         <v>23</v>
@@ -42267,7 +42267,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" customHeight="1" spans="1:28">
+    <row r="33" ht="13.5" customHeight="1" spans="1:28">
       <c r="A33" s="24"/>
       <c r="B33" s="25">
         <v>24</v>
@@ -42353,7 +42353,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="34" customHeight="1" spans="1:28">
+    <row r="34" ht="13.5" customHeight="1" spans="1:28">
       <c r="A34" s="24"/>
       <c r="B34" s="25">
         <v>25</v>
@@ -42439,7 +42439,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="35" customHeight="1" spans="1:28">
+    <row r="35" ht="13.5" customHeight="1" spans="1:28">
       <c r="A35" s="24"/>
       <c r="B35" s="25">
         <v>26</v>
@@ -42525,7 +42525,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="36" customHeight="1" spans="1:28">
+    <row r="36" ht="13.5" customHeight="1" spans="1:28">
       <c r="A36" s="24"/>
       <c r="B36" s="25">
         <v>27</v>
@@ -42611,7 +42611,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="37" customHeight="1" spans="1:28">
+    <row r="37" ht="13.5" customHeight="1" spans="1:28">
       <c r="A37" s="24"/>
       <c r="B37" s="25">
         <v>28</v>
@@ -42697,7 +42697,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="38" customHeight="1" spans="1:28">
+    <row r="38" ht="13.5" customHeight="1" spans="1:28">
       <c r="A38" s="24"/>
       <c r="B38" s="25">
         <v>29</v>
@@ -42783,7 +42783,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="39" customHeight="1" spans="1:28">
+    <row r="39" ht="13.5" customHeight="1" spans="1:28">
       <c r="A39" s="24"/>
       <c r="B39" s="25">
         <v>30</v>
@@ -42869,7 +42869,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="40" customHeight="1" spans="1:28">
+    <row r="40" ht="13.5" customHeight="1" spans="1:28">
       <c r="A40" s="24"/>
       <c r="B40" s="25">
         <v>31</v>
@@ -42955,7 +42955,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="41" customHeight="1" spans="1:28">
+    <row r="41" ht="13.5" customHeight="1" spans="1:28">
       <c r="A41" s="24"/>
       <c r="B41" s="25">
         <v>32</v>
@@ -43041,7 +43041,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="42" customHeight="1" spans="1:28">
+    <row r="42" ht="13.5" customHeight="1" spans="1:28">
       <c r="A42" s="15" t="s">
         <v>33</v>
       </c>
@@ -43129,7 +43129,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="43" customHeight="1" spans="1:28">
+    <row r="43" ht="13.5" customHeight="1" spans="1:28">
       <c r="A43" s="15"/>
       <c r="B43" s="14">
         <v>2</v>
@@ -43215,7 +43215,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="44" customHeight="1" spans="1:28">
+    <row r="44" ht="13.5" customHeight="1" spans="1:28">
       <c r="A44" s="15"/>
       <c r="B44" s="14">
         <v>3</v>
@@ -43301,7 +43301,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="45" customHeight="1" spans="1:28">
+    <row r="45" ht="13.5" customHeight="1" spans="1:28">
       <c r="A45" s="20" t="s">
         <v>59</v>
       </c>
@@ -43389,7 +43389,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="46" customFormat="1" customHeight="1" spans="1:28">
+    <row r="46" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A46" s="28"/>
       <c r="B46" s="22">
         <v>13</v>
@@ -43475,7 +43475,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="47" customFormat="1" customHeight="1" spans="1:28">
+    <row r="47" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A47" s="28"/>
       <c r="B47" s="22">
         <v>14</v>
@@ -43561,7 +43561,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="48" customFormat="1" customHeight="1" spans="1:28">
+    <row r="48" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A48" s="28"/>
       <c r="B48" s="22">
         <v>15</v>
@@ -43647,7 +43647,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="49" customFormat="1" customHeight="1" spans="1:28">
+    <row r="49" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A49" s="28"/>
       <c r="B49" s="22">
         <v>16</v>
@@ -43733,7 +43733,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="50" customFormat="1" customHeight="1" spans="1:28">
+    <row r="50" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A50" s="28"/>
       <c r="B50" s="22">
         <v>17</v>
@@ -43819,7 +43819,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="51" customFormat="1" customHeight="1" spans="1:28">
+    <row r="51" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A51" s="28"/>
       <c r="B51" s="22">
         <v>18</v>
@@ -43905,7 +43905,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="52" customFormat="1" customHeight="1" spans="1:28">
+    <row r="52" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A52" s="28"/>
       <c r="B52" s="22">
         <v>19</v>
@@ -43991,7 +43991,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="53" customFormat="1" customHeight="1" spans="1:28">
+    <row r="53" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A53" s="15" t="s">
         <v>28</v>
       </c>
@@ -44079,7 +44079,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="54" customFormat="1" customHeight="1" spans="1:28">
+    <row r="54" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A54" s="15"/>
       <c r="B54" s="16">
         <v>9</v>
@@ -44165,7 +44165,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="55" customFormat="1" customHeight="1" spans="1:28">
+    <row r="55" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A55" s="15"/>
       <c r="B55" s="16">
         <v>10</v>
@@ -44251,7 +44251,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="56" customFormat="1" customHeight="1" spans="1:28">
+    <row r="56" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A56" s="15" t="s">
         <v>31</v>
       </c>
@@ -44339,7 +44339,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="57" customFormat="1" customHeight="1" spans="1:28">
+    <row r="57" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A57" s="15"/>
       <c r="B57" s="16">
         <v>19</v>
@@ -44425,7 +44425,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="58" customFormat="1" customHeight="1" spans="1:28">
+    <row r="58" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A58" s="15"/>
       <c r="B58" s="16">
         <v>20</v>
@@ -44511,7 +44511,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="59" customFormat="1" customHeight="1" spans="1:28">
+    <row r="59" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A59" s="15"/>
       <c r="B59" s="16">
         <v>21</v>
@@ -44597,7 +44597,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="60" customFormat="1" customHeight="1" spans="1:28">
+    <row r="60" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A60" s="15"/>
       <c r="B60" s="16">
         <v>22</v>
@@ -44683,7 +44683,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="61" customFormat="1" customHeight="1" spans="1:28">
+    <row r="61" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A61" s="15"/>
       <c r="B61" s="16">
         <v>23</v>
@@ -44769,7 +44769,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="62" customFormat="1" customHeight="1" spans="1:28">
+    <row r="62" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A62" s="15"/>
       <c r="B62" s="16">
         <v>24</v>
@@ -44855,7 +44855,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="63" customFormat="1" customHeight="1" spans="1:28">
+    <row r="63" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A63" s="15" t="s">
         <v>45</v>
       </c>
@@ -44943,7 +44943,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="64" customFormat="1" customHeight="1" spans="1:28">
+    <row r="64" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A64" s="15"/>
       <c r="B64" s="16">
         <v>16</v>
@@ -45029,7 +45029,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="65" customFormat="1" customHeight="1" spans="1:28">
+    <row r="65" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A65" s="24"/>
       <c r="B65" s="16">
         <v>17</v>
@@ -45115,7 +45115,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="66" customFormat="1" customHeight="1" spans="1:28">
+    <row r="66" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A66" s="24"/>
       <c r="B66" s="16">
         <v>18</v>
@@ -45201,7 +45201,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="67" customFormat="1" customHeight="1" spans="1:28">
+    <row r="67" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A67" s="15" t="s">
         <v>33</v>
       </c>
@@ -45289,7 +45289,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="68" customFormat="1" customHeight="1" spans="1:28">
+    <row r="68" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A68" s="15"/>
       <c r="B68" s="16">
         <v>5</v>
@@ -45375,7 +45375,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="69" customFormat="1" customHeight="1" spans="1:28">
+    <row r="69" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A69" s="15"/>
       <c r="B69" s="16">
         <v>6</v>
@@ -45461,7 +45461,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="70" customFormat="1" customHeight="1" spans="1:28">
+    <row r="70" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A70" s="31" t="s">
         <v>34</v>
       </c>
@@ -45549,7 +45549,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="71" customFormat="1" customHeight="1" spans="1:28">
+    <row r="71" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A71" s="31"/>
       <c r="B71" s="23">
         <v>10</v>
@@ -45635,7 +45635,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="72" customFormat="1" customHeight="1" spans="1:28">
+    <row r="72" customFormat="1" ht="13.5" customHeight="1" spans="1:28">
       <c r="A72" s="31"/>
       <c r="B72" s="23">
         <v>11</v>
@@ -45832,7 +45832,7 @@
       <c r="A74" s="31"/>
       <c r="B74" s="23"/>
       <c r="C74" s="12">
-        <f t="shared" ref="C74:Z74" si="5">_xlfn.STDEV.S(C3:C72)</f>
+        <f t="shared" ref="C74:AA74" si="5">_xlfn.STDEV.S(C3:C72)</f>
         <v>0.167801519350929</v>
       </c>
       <c r="D74" s="12">
@@ -45928,7 +45928,7 @@
         <v>0.239045721866879</v>
       </c>
       <c r="AA74" s="12">
-        <f>_xlfn.STDEV.S(AA3:AA72)</f>
+        <f t="shared" si="5"/>
         <v>1.27729009206839</v>
       </c>
       <c r="AB74" s="11" t="s">
@@ -46506,9 +46506,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C53"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9.02727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="23.4336283185841" customWidth="1"/>
+    <col min="1" max="1" width="23.4363636363636" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -47054,13 +47054,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AA80"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.02727272727273" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="24" width="12.7964601769912"/>
-    <col min="26" max="27" width="12.7964601769912"/>
+    <col min="2" max="24" width="12.8"/>
+    <col min="26" max="27" width="12.8"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:27">
+    <row r="1" s="1" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -47228,7 +47228,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" customHeight="1" spans="1:27">
+    <row r="3" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A3" s="13"/>
       <c r="B3" s="14">
         <v>4</v>
@@ -47311,7 +47311,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" customHeight="1" spans="1:27">
+    <row r="4" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A4" s="13"/>
       <c r="B4" s="14">
         <v>5</v>
@@ -47394,7 +47394,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:27">
+    <row r="5" ht="13.5" customHeight="1" spans="1:27">
       <c r="A5" s="15"/>
       <c r="B5" s="14">
         <v>14</v>
@@ -47477,7 +47477,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:27">
+    <row r="6" ht="13.5" customHeight="1" spans="1:27">
       <c r="A6" s="15"/>
       <c r="B6" s="14">
         <v>15</v>
@@ -47560,7 +47560,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:27">
+    <row r="7" ht="13.5" customHeight="1" spans="1:27">
       <c r="A7" s="15"/>
       <c r="B7" s="14">
         <v>16</v>
@@ -47643,7 +47643,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:27">
+    <row r="8" ht="13.5" customHeight="1" spans="1:27">
       <c r="A8" s="15"/>
       <c r="B8" s="14">
         <v>17</v>
@@ -47726,7 +47726,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:27">
+    <row r="9" ht="13.5" customHeight="1" spans="1:27">
       <c r="A9" s="15"/>
       <c r="B9" s="16">
         <v>18</v>
@@ -47809,7 +47809,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:27">
+    <row r="10" ht="13.5" customHeight="1" spans="1:27">
       <c r="A10" s="15"/>
       <c r="B10" s="16">
         <v>19</v>
@@ -47892,7 +47892,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:27">
+    <row r="11" ht="13.5" customHeight="1" spans="1:27">
       <c r="A11" s="15"/>
       <c r="B11" s="16">
         <v>20</v>
@@ -47975,7 +47975,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:27">
+    <row r="12" ht="13.5" customHeight="1" spans="1:27">
       <c r="C12">
         <f>AVERAGE(C2:C8)</f>
         <v>4.85714285714286</v>
@@ -48077,8 +48077,8 @@
         <v>68.5714285714286</v>
       </c>
     </row>
-    <row r="13" customHeight="1"/>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:27">
+    <row r="13" ht="13.5" customHeight="1"/>
+    <row r="14" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A14" s="9" t="s">
         <v>31</v>
       </c>
@@ -48163,7 +48163,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:27">
+    <row r="15" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A15" s="13"/>
       <c r="B15" s="14">
         <v>2</v>
@@ -48246,7 +48246,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="1:27">
+    <row r="16" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A16" s="13"/>
       <c r="B16" s="14">
         <v>6</v>
@@ -48329,7 +48329,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="1:27">
+    <row r="17" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A17" s="13"/>
       <c r="B17" s="14">
         <v>7</v>
@@ -48412,7 +48412,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="1:27">
+    <row r="18" ht="13.5" customHeight="1" spans="1:27">
       <c r="A18" s="13"/>
       <c r="B18" s="14">
         <v>17</v>
@@ -48495,7 +48495,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="1:27">
+    <row r="19" ht="13.5" customHeight="1" spans="1:27">
       <c r="A19" s="13"/>
       <c r="B19" s="14">
         <v>26</v>
@@ -48578,7 +48578,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="1:27">
+    <row r="20" ht="13.5" customHeight="1" spans="1:27">
       <c r="A20" s="13"/>
       <c r="B20" s="14">
         <v>27</v>
@@ -48661,7 +48661,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="1:27">
+    <row r="21" ht="13.5" customHeight="1" spans="1:27">
       <c r="A21" s="13"/>
       <c r="B21" s="14">
         <v>28</v>
@@ -48744,7 +48744,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="1:27">
+    <row r="22" ht="13.5" customHeight="1" spans="1:27">
       <c r="A22" s="13"/>
       <c r="B22" s="14">
         <v>29</v>
@@ -48827,7 +48827,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="1:27">
+    <row r="23" ht="13.5" customHeight="1" spans="1:27">
       <c r="A23" s="13"/>
       <c r="B23" s="14">
         <v>30</v>
@@ -48910,7 +48910,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="1:27">
+    <row r="24" ht="13.5" customHeight="1" spans="1:27">
       <c r="A24" s="13"/>
       <c r="B24" s="14">
         <v>31</v>
@@ -48993,7 +48993,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="1:27">
+    <row r="25" ht="13.5" customHeight="1" spans="1:27">
       <c r="A25" s="13"/>
       <c r="B25" s="14">
         <v>32</v>
@@ -49076,7 +49076,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="1:27">
+    <row r="26" ht="13.5" customHeight="1" spans="1:27">
       <c r="A26" s="13"/>
       <c r="B26" s="14">
         <v>33</v>
@@ -49159,7 +49159,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="1:27">
+    <row r="27" ht="13.5" customHeight="1" spans="1:27">
       <c r="A27" s="13"/>
       <c r="B27" s="14">
         <v>34</v>
@@ -49242,7 +49242,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="1:27">
+    <row r="28" ht="13.5" customHeight="1" spans="1:27">
       <c r="A28" s="13"/>
       <c r="B28" s="14">
         <v>35</v>
@@ -49325,7 +49325,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="1:27">
+    <row r="29" ht="13.5" customHeight="1" spans="1:27">
       <c r="A29" s="13"/>
       <c r="B29" s="14">
         <v>36</v>
@@ -49408,7 +49408,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="1:27">
+    <row r="30" ht="13.5" customHeight="1" spans="1:27">
       <c r="A30" s="13"/>
       <c r="B30" s="14">
         <v>37</v>
@@ -49491,7 +49491,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="1:27">
+    <row r="31" ht="13.5" customHeight="1" spans="1:27">
       <c r="A31" s="13"/>
       <c r="B31" s="14">
         <v>38</v>
@@ -49574,7 +49574,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="1:27">
+    <row r="32" ht="13.5" customHeight="1" spans="1:27">
       <c r="A32" s="13"/>
       <c r="B32" s="16">
         <v>44</v>
@@ -49657,7 +49657,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="33" customHeight="1" spans="1:27">
+    <row r="33" ht="13.5" customHeight="1" spans="1:27">
       <c r="A33" s="13"/>
       <c r="B33" s="16">
         <v>45</v>
@@ -49740,7 +49740,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="34" customHeight="1" spans="1:27">
+    <row r="34" ht="13.5" customHeight="1" spans="1:27">
       <c r="A34" s="13"/>
       <c r="B34" s="16">
         <v>46</v>
@@ -49823,7 +49823,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="35" customHeight="1" spans="1:27">
+    <row r="35" ht="13.5" customHeight="1" spans="1:27">
       <c r="A35" s="13"/>
       <c r="B35" s="16">
         <v>47</v>
@@ -49906,7 +49906,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="36" customHeight="1" spans="1:27">
+    <row r="36" ht="13.5" customHeight="1" spans="1:27">
       <c r="A36" s="13"/>
       <c r="B36" s="16">
         <v>48</v>
@@ -49989,7 +49989,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="37" customHeight="1" spans="1:27">
+    <row r="37" ht="13.5" customHeight="1" spans="1:27">
       <c r="A37" s="13"/>
       <c r="B37" s="16">
         <v>49</v>
@@ -50072,7 +50072,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="38" customHeight="1" spans="1:27">
+    <row r="38" ht="13.5" customHeight="1" spans="1:27">
       <c r="A38" s="13"/>
       <c r="B38" s="16">
         <v>50</v>
@@ -50155,7 +50155,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="39" customHeight="1" spans="1:27">
+    <row r="39" ht="13.5" customHeight="1" spans="1:27">
       <c r="A39" s="30"/>
       <c r="B39" s="10"/>
       <c r="C39" s="26">
@@ -50259,8 +50259,8 @@
         <v>70.5</v>
       </c>
     </row>
-    <row r="40" customHeight="1"/>
-    <row r="41" customFormat="1" customHeight="1" spans="1:27">
+    <row r="40" ht="13.5" customHeight="1"/>
+    <row r="41" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A41" s="30" t="s">
         <v>32</v>
       </c>
@@ -50345,7 +50345,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="42" customFormat="1" customHeight="1" spans="1:27">
+    <row r="42" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A42" s="15"/>
       <c r="B42" s="10">
         <v>2</v>
@@ -50428,7 +50428,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="43" customFormat="1" customHeight="1" spans="1:27">
+    <row r="43" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A43" s="15"/>
       <c r="B43" s="10">
         <v>3</v>
@@ -50511,7 +50511,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="44" customFormat="1" customHeight="1" spans="1:27">
+    <row r="44" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A44" s="15"/>
       <c r="B44" s="10">
         <v>4</v>
@@ -50594,7 +50594,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="45" customFormat="1" customHeight="1" spans="1:27">
+    <row r="45" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A45" s="15"/>
       <c r="B45" s="10">
         <v>5</v>
@@ -50677,7 +50677,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="46" customFormat="1" customHeight="1" spans="1:27">
+    <row r="46" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A46" s="15"/>
       <c r="B46" s="10">
         <v>6</v>
@@ -50760,7 +50760,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="47" customFormat="1" customHeight="1" spans="1:27">
+    <row r="47" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A47" s="15"/>
       <c r="B47" s="10">
         <v>7</v>
@@ -50843,7 +50843,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="48" customFormat="1" customHeight="1" spans="1:27">
+    <row r="48" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A48" s="15"/>
       <c r="B48" s="10">
         <v>8</v>
@@ -50926,7 +50926,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="49" customFormat="1" customHeight="1" spans="1:27">
+    <row r="49" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A49" s="15"/>
       <c r="B49" s="10">
         <v>9</v>
@@ -51009,7 +51009,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="50" customFormat="1" customHeight="1" spans="1:27">
+    <row r="50" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A50" s="15"/>
       <c r="B50" s="10">
         <v>10</v>
@@ -51092,7 +51092,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="51" customFormat="1" customHeight="1" spans="1:27">
+    <row r="51" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A51" s="15"/>
       <c r="B51" s="10">
         <v>11</v>
@@ -51175,7 +51175,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="52" customFormat="1" customHeight="1" spans="1:27">
+    <row r="52" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A52" s="15"/>
       <c r="B52" s="10">
         <v>12</v>
@@ -51258,7 +51258,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="53" customFormat="1" customHeight="1" spans="1:27">
+    <row r="53" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A53" s="15"/>
       <c r="B53" s="10">
         <v>13</v>
@@ -51341,7 +51341,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="54" customFormat="1" customHeight="1" spans="1:27">
+    <row r="54" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A54" s="15"/>
       <c r="B54" s="10">
         <v>14</v>
@@ -51424,7 +51424,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="55" customFormat="1" customHeight="1" spans="1:27">
+    <row r="55" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A55" s="15"/>
       <c r="B55" s="16">
         <v>33</v>
@@ -51507,7 +51507,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="56" customFormat="1" customHeight="1" spans="1:27">
+    <row r="56" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A56" s="15"/>
       <c r="B56" s="16">
         <v>34</v>
@@ -51590,7 +51590,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="57" customFormat="1" customHeight="1" spans="1:27">
+    <row r="57" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A57" s="24"/>
       <c r="B57" s="16">
         <v>35</v>
@@ -51673,7 +51673,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="58" customFormat="1" customHeight="1" spans="1:27">
+    <row r="58" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A58" s="24"/>
       <c r="B58" s="16">
         <v>36</v>
@@ -51756,7 +51756,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="59" customHeight="1" spans="1:27">
+    <row r="59" ht="13.5" customHeight="1" spans="1:27">
       <c r="C59">
         <f>AVERAGE(C41:C54)</f>
         <v>4.92857142857143</v>
@@ -51858,8 +51858,8 @@
         <v>70.4285714285714</v>
       </c>
     </row>
-    <row r="60" customHeight="1"/>
-    <row r="61" customHeight="1" spans="1:27">
+    <row r="60" ht="13.5" customHeight="1"/>
+    <row r="61" ht="13.5" customHeight="1" spans="1:27">
       <c r="A61" s="15" t="s">
         <v>33</v>
       </c>
@@ -51944,7 +51944,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="62" customHeight="1" spans="1:27">
+    <row r="62" ht="13.5" customHeight="1" spans="1:27">
       <c r="A62" s="15"/>
       <c r="B62" s="14">
         <v>8</v>
@@ -52027,7 +52027,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="63" customHeight="1" spans="1:27">
+    <row r="63" ht="13.5" customHeight="1" spans="1:27">
       <c r="A63" s="24"/>
       <c r="B63" s="14">
         <v>9</v>
@@ -52110,7 +52110,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="64" customHeight="1" spans="1:27">
+    <row r="64" ht="13.5" customHeight="1" spans="1:27">
       <c r="A64" s="15"/>
       <c r="B64" s="16">
         <v>10</v>
@@ -52193,7 +52193,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="65" customHeight="1" spans="1:27">
+    <row r="65" ht="13.5" customHeight="1" spans="1:27">
       <c r="A65" s="15"/>
       <c r="B65" s="16">
         <v>11</v>
@@ -52276,7 +52276,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="66" customHeight="1" spans="1:27">
+    <row r="66" ht="13.5" customHeight="1" spans="1:27">
       <c r="A66" s="15"/>
       <c r="B66" s="16">
         <v>12</v>
@@ -52359,7 +52359,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="67" customHeight="1" spans="1:27">
+    <row r="67" ht="13.5" customHeight="1" spans="1:27">
       <c r="C67">
         <f>AVERAGE(C61:C63)</f>
         <v>5</v>
@@ -52461,8 +52461,8 @@
         <v>71.3333333333333</v>
       </c>
     </row>
-    <row r="68" customHeight="1"/>
-    <row r="69" customHeight="1" spans="1:27">
+    <row r="68" ht="13.5" customHeight="1"/>
+    <row r="69" ht="13.5" customHeight="1" spans="1:27">
       <c r="A69" s="20" t="s">
         <v>34</v>
       </c>
@@ -52547,7 +52547,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="70" customHeight="1" spans="1:27">
+    <row r="70" ht="13.5" customHeight="1" spans="1:27">
       <c r="A70" s="20"/>
       <c r="B70" s="21">
         <v>3</v>
@@ -52630,7 +52630,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="71" customHeight="1" spans="1:27">
+    <row r="71" ht="13.5" customHeight="1" spans="1:27">
       <c r="A71" s="20"/>
       <c r="B71" s="21">
         <v>4</v>
@@ -52713,7 +52713,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="72" customHeight="1" spans="1:27">
+    <row r="72" ht="13.5" customHeight="1" spans="1:27">
       <c r="A72" s="20"/>
       <c r="B72" s="21">
         <v>5</v>
@@ -52795,7 +52795,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="73" customHeight="1" spans="1:27">
+    <row r="73" ht="13.5" customHeight="1" spans="1:27">
       <c r="A73" s="20"/>
       <c r="B73" s="21">
         <v>6</v>
@@ -52878,7 +52878,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="74" customHeight="1" spans="1:27">
+    <row r="74" ht="13.5" customHeight="1" spans="1:27">
       <c r="A74" s="20"/>
       <c r="B74" s="21">
         <v>7</v>
@@ -52961,7 +52961,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="75" customHeight="1" spans="1:27">
+    <row r="75" ht="13.5" customHeight="1" spans="1:27">
       <c r="A75" s="20"/>
       <c r="B75" s="21">
         <v>8</v>
@@ -53044,7 +53044,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="76" customFormat="1" customHeight="1" spans="1:27">
+    <row r="76" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A76" s="28"/>
       <c r="B76" s="22">
         <v>12</v>
@@ -53127,7 +53127,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="77" customFormat="1" customHeight="1" spans="1:27">
+    <row r="77" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A77" s="31"/>
       <c r="B77" s="23">
         <v>20</v>
@@ -53210,7 +53210,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="78" customFormat="1" customHeight="1" spans="1:27">
+    <row r="78" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A78" s="32"/>
       <c r="B78" s="23">
         <v>21</v>
@@ -53293,7 +53293,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="79" customFormat="1" customHeight="1" spans="1:27">
+    <row r="79" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A79" s="31"/>
       <c r="B79" s="23">
         <v>22</v>
@@ -53376,7 +53376,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="80" customHeight="1" spans="1:27">
+    <row r="80" ht="13.5" customHeight="1" spans="1:27">
       <c r="C80">
         <f>AVERAGE(C69:C76)</f>
         <v>5</v>
@@ -53497,18 +53497,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AA81"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.02727272727273" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="3" width="12.7964601769912"/>
-    <col min="5" max="6" width="12.7964601769912"/>
-    <col min="9" max="9" width="12.7964601769912"/>
-    <col min="11" max="18" width="12.7964601769912"/>
-    <col min="20" max="20" width="12.7964601769912"/>
-    <col min="22" max="24" width="12.7964601769912"/>
-    <col min="26" max="27" width="12.7964601769912"/>
+    <col min="2" max="3" width="12.8"/>
+    <col min="5" max="6" width="12.8"/>
+    <col min="9" max="9" width="12.8"/>
+    <col min="11" max="18" width="12.8"/>
+    <col min="20" max="20" width="12.8"/>
+    <col min="22" max="24" width="12.8"/>
+    <col min="26" max="27" width="12.8"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:27">
+    <row r="1" s="1" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A1" s="3" t="s">
         <v>43</v>
       </c>
@@ -53539,7 +53539,7 @@
       <c r="Z1" s="4"/>
       <c r="AA1" s="5"/>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:27">
+    <row r="2" s="1" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -53622,7 +53622,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" customHeight="1" spans="1:27">
+    <row r="3" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A3" s="9" t="s">
         <v>28</v>
       </c>
@@ -53707,7 +53707,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" customHeight="1" spans="1:27">
+    <row r="4" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A4" s="13"/>
       <c r="B4" s="14">
         <v>2</v>
@@ -53790,7 +53790,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" customHeight="1" spans="1:27">
+    <row r="5" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A5" s="13"/>
       <c r="B5" s="14">
         <v>6</v>
@@ -53873,7 +53873,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:27">
+    <row r="6" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A6" s="13"/>
       <c r="B6" s="14">
         <v>7</v>
@@ -53956,7 +53956,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:27">
+    <row r="7" ht="13.5" customHeight="1" spans="1:27">
       <c r="A7" s="15"/>
       <c r="B7" s="14">
         <v>11</v>
@@ -54039,7 +54039,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:27">
+    <row r="8" ht="13.5" customHeight="1" spans="1:27">
       <c r="A8" s="15"/>
       <c r="B8" s="14">
         <v>12</v>
@@ -54122,7 +54122,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:27">
+    <row r="9" ht="13.5" customHeight="1" spans="1:27">
       <c r="A9" s="15"/>
       <c r="B9" s="14">
         <v>13</v>
@@ -54205,7 +54205,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:27">
+    <row r="10" ht="13.5" customHeight="1" spans="1:27">
       <c r="A10" s="15"/>
       <c r="B10" s="16">
         <v>8</v>
@@ -54288,7 +54288,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:27">
+    <row r="11" ht="13.5" customHeight="1" spans="1:27">
       <c r="A11" s="15"/>
       <c r="B11" s="16">
         <v>9</v>
@@ -54371,7 +54371,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:27">
+    <row r="12" ht="13.5" customHeight="1" spans="1:27">
       <c r="A12" s="15"/>
       <c r="B12" s="16">
         <v>10</v>
@@ -54454,7 +54454,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:27">
+    <row r="13" ht="13.5" customHeight="1" spans="1:27">
       <c r="C13">
         <f>AVERAGE(C3:C12)</f>
         <v>5</v>
@@ -54556,8 +54556,8 @@
         <v>70.3</v>
       </c>
     </row>
-    <row r="14" customHeight="1"/>
-    <row r="15" customHeight="1" spans="1:27">
+    <row r="14" ht="13.5" customHeight="1"/>
+    <row r="15" ht="13.5" customHeight="1" spans="1:27">
       <c r="A15" s="15" t="s">
         <v>31</v>
       </c>
@@ -54642,7 +54642,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:27">
+    <row r="16" ht="13.5" customHeight="1" spans="1:27">
       <c r="A16" s="15"/>
       <c r="B16" s="14">
         <v>4</v>
@@ -54725,7 +54725,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:27">
+    <row r="17" ht="13.5" customHeight="1" spans="1:27">
       <c r="A17" s="15"/>
       <c r="B17" s="14">
         <v>5</v>
@@ -54808,7 +54808,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="1:27">
+    <row r="18" ht="13.5" customHeight="1" spans="1:27">
       <c r="A18" s="15"/>
       <c r="B18" s="14">
         <v>8</v>
@@ -54891,7 +54891,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="1:27">
+    <row r="19" ht="13.5" customHeight="1" spans="1:27">
       <c r="A19" s="15"/>
       <c r="B19" s="14">
         <v>9</v>
@@ -54974,7 +54974,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="1:27">
+    <row r="20" ht="13.5" customHeight="1" spans="1:27">
       <c r="A20" s="15"/>
       <c r="B20" s="14">
         <v>10</v>
@@ -55057,7 +55057,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="1:27">
+    <row r="21" ht="13.5" customHeight="1" spans="1:27">
       <c r="A21" s="15"/>
       <c r="B21" s="14">
         <v>11</v>
@@ -55140,7 +55140,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="1:27">
+    <row r="22" ht="13.5" customHeight="1" spans="1:27">
       <c r="A22" s="15"/>
       <c r="B22" s="14">
         <v>12</v>
@@ -55223,7 +55223,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="1:27">
+    <row r="23" ht="13.5" customHeight="1" spans="1:27">
       <c r="A23" s="15"/>
       <c r="B23" s="14">
         <v>13</v>
@@ -55306,7 +55306,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="1:27">
+    <row r="24" ht="13.5" customHeight="1" spans="1:27">
       <c r="A24" s="15"/>
       <c r="B24" s="14">
         <v>14</v>
@@ -55389,7 +55389,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="1:27">
+    <row r="25" ht="13.5" customHeight="1" spans="1:27">
       <c r="A25" s="15"/>
       <c r="B25" s="14">
         <v>15</v>
@@ -55472,7 +55472,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="1:27">
+    <row r="26" ht="13.5" customHeight="1" spans="1:27">
       <c r="A26" s="15"/>
       <c r="B26" s="14">
         <v>16</v>
@@ -55555,7 +55555,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="1:27">
+    <row r="27" ht="13.5" customHeight="1" spans="1:27">
       <c r="A27" s="15"/>
       <c r="B27" s="14">
         <v>25</v>
@@ -55638,7 +55638,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="1:27">
+    <row r="28" ht="13.5" customHeight="1" spans="1:27">
       <c r="A28" s="15"/>
       <c r="B28" s="14">
         <v>39</v>
@@ -55721,7 +55721,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="1:27">
+    <row r="29" ht="13.5" customHeight="1" spans="1:27">
       <c r="A29" s="15"/>
       <c r="B29" s="14">
         <v>40</v>
@@ -55804,7 +55804,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="1:27">
+    <row r="30" ht="13.5" customHeight="1" spans="1:27">
       <c r="A30" s="15"/>
       <c r="B30" s="14">
         <v>41</v>
@@ -55887,7 +55887,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="1:27">
+    <row r="31" ht="13.5" customHeight="1" spans="1:27">
       <c r="A31" s="15"/>
       <c r="B31" s="14">
         <v>42</v>
@@ -55970,7 +55970,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="1:27">
+    <row r="32" ht="13.5" customHeight="1" spans="1:27">
       <c r="A32" s="15"/>
       <c r="B32" s="14">
         <v>43</v>
@@ -56053,7 +56053,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="33" customHeight="1" spans="1:27">
+    <row r="33" ht="13.5" customHeight="1" spans="1:27">
       <c r="A33" s="15"/>
       <c r="B33" s="16">
         <v>18</v>
@@ -56136,7 +56136,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="34" customHeight="1" spans="1:27">
+    <row r="34" ht="13.5" customHeight="1" spans="1:27">
       <c r="A34" s="15"/>
       <c r="B34" s="16">
         <v>19</v>
@@ -56219,7 +56219,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35" customHeight="1" spans="1:27">
+    <row r="35" ht="13.5" customHeight="1" spans="1:27">
       <c r="A35" s="15"/>
       <c r="B35" s="16">
         <v>20</v>
@@ -56302,7 +56302,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" customHeight="1" spans="1:27">
+    <row r="36" ht="13.5" customHeight="1" spans="1:27">
       <c r="A36" s="15"/>
       <c r="B36" s="16">
         <v>21</v>
@@ -56385,7 +56385,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" customHeight="1" spans="1:27">
+    <row r="37" ht="13.5" customHeight="1" spans="1:27">
       <c r="A37" s="15"/>
       <c r="B37" s="16">
         <v>22</v>
@@ -56468,7 +56468,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="38" customHeight="1" spans="1:27">
+    <row r="38" ht="13.5" customHeight="1" spans="1:27">
       <c r="A38" s="15"/>
       <c r="B38" s="16">
         <v>23</v>
@@ -56551,7 +56551,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="39" customHeight="1" spans="1:27">
+    <row r="39" ht="13.5" customHeight="1" spans="1:27">
       <c r="A39" s="15"/>
       <c r="B39" s="16">
         <v>24</v>
@@ -56634,7 +56634,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" customHeight="1" spans="1:27">
+    <row r="40" ht="13.5" customHeight="1" spans="1:27">
       <c r="C40">
         <f>AVERAGE(C15:C39)</f>
         <v>4.92</v>
@@ -56736,8 +56736,8 @@
         <v>71.16</v>
       </c>
     </row>
-    <row r="41" customHeight="1"/>
-    <row r="42" customHeight="1" spans="1:27">
+    <row r="41" ht="13.5" customHeight="1"/>
+    <row r="42" ht="13.5" customHeight="1" spans="1:27">
       <c r="A42" s="24" t="s">
         <v>45</v>
       </c>
@@ -56822,7 +56822,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="43" customHeight="1" spans="1:27">
+    <row r="43" ht="13.5" customHeight="1" spans="1:27">
       <c r="A43" s="24"/>
       <c r="B43" s="25">
         <v>20</v>
@@ -56905,7 +56905,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="44" customHeight="1" spans="1:27">
+    <row r="44" ht="13.5" customHeight="1" spans="1:27">
       <c r="A44" s="24"/>
       <c r="B44" s="25">
         <v>21</v>
@@ -56988,7 +56988,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="45" customHeight="1" spans="1:27">
+    <row r="45" ht="13.5" customHeight="1" spans="1:27">
       <c r="A45" s="24"/>
       <c r="B45" s="25">
         <v>22</v>
@@ -57071,7 +57071,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="46" customHeight="1" spans="1:27">
+    <row r="46" ht="13.5" customHeight="1" spans="1:27">
       <c r="A46" s="24"/>
       <c r="B46" s="25">
         <v>23</v>
@@ -57154,7 +57154,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="47" customHeight="1" spans="1:27">
+    <row r="47" ht="13.5" customHeight="1" spans="1:27">
       <c r="A47" s="24"/>
       <c r="B47" s="25">
         <v>24</v>
@@ -57237,7 +57237,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="48" customHeight="1" spans="1:27">
+    <row r="48" ht="13.5" customHeight="1" spans="1:27">
       <c r="A48" s="24"/>
       <c r="B48" s="25">
         <v>25</v>
@@ -57320,7 +57320,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="49" customHeight="1" spans="1:27">
+    <row r="49" ht="13.5" customHeight="1" spans="1:27">
       <c r="A49" s="24"/>
       <c r="B49" s="25">
         <v>26</v>
@@ -57403,7 +57403,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="50" customHeight="1" spans="1:27">
+    <row r="50" ht="13.5" customHeight="1" spans="1:27">
       <c r="A50" s="24"/>
       <c r="B50" s="25">
         <v>27</v>
@@ -57486,7 +57486,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="51" customHeight="1" spans="1:27">
+    <row r="51" ht="13.5" customHeight="1" spans="1:27">
       <c r="A51" s="24"/>
       <c r="B51" s="25">
         <v>28</v>
@@ -57569,7 +57569,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="52" customHeight="1" spans="1:27">
+    <row r="52" ht="13.5" customHeight="1" spans="1:27">
       <c r="A52" s="24"/>
       <c r="B52" s="25">
         <v>29</v>
@@ -57652,7 +57652,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="53" customHeight="1" spans="1:27">
+    <row r="53" ht="13.5" customHeight="1" spans="1:27">
       <c r="A53" s="24"/>
       <c r="B53" s="25">
         <v>30</v>
@@ -57735,7 +57735,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="54" customHeight="1" spans="1:27">
+    <row r="54" ht="13.5" customHeight="1" spans="1:27">
       <c r="A54" s="24"/>
       <c r="B54" s="25">
         <v>31</v>
@@ -57818,7 +57818,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="55" customHeight="1" spans="1:27">
+    <row r="55" ht="13.5" customHeight="1" spans="1:27">
       <c r="A55" s="24"/>
       <c r="B55" s="25">
         <v>32</v>
@@ -57901,7 +57901,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="56" customHeight="1" spans="1:27">
+    <row r="56" ht="13.5" customHeight="1" spans="1:27">
       <c r="A56" s="15"/>
       <c r="B56" s="16">
         <v>15</v>
@@ -57984,7 +57984,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="57" customHeight="1" spans="1:27">
+    <row r="57" ht="13.5" customHeight="1" spans="1:27">
       <c r="A57" s="15"/>
       <c r="B57" s="16">
         <v>16</v>
@@ -58067,7 +58067,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="58" customHeight="1" spans="1:27">
+    <row r="58" ht="13.5" customHeight="1" spans="1:27">
       <c r="A58" s="24"/>
       <c r="B58" s="16">
         <v>17</v>
@@ -58150,7 +58150,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="59" customHeight="1" spans="1:27">
+    <row r="59" ht="13.5" customHeight="1" spans="1:27">
       <c r="A59" s="24"/>
       <c r="B59" s="16">
         <v>18</v>
@@ -58233,7 +58233,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="60" customHeight="1" spans="1:27">
+    <row r="60" ht="13.5" customHeight="1" spans="1:27">
       <c r="C60">
         <f>AVERAGE(C42:C59)</f>
         <v>5</v>
@@ -58335,8 +58335,8 @@
         <v>70.6666666666667</v>
       </c>
     </row>
-    <row r="61" customHeight="1"/>
-    <row r="62" customHeight="1" spans="1:27">
+    <row r="61" ht="13.5" customHeight="1"/>
+    <row r="62" ht="13.5" customHeight="1" spans="1:27">
       <c r="A62" s="15" t="s">
         <v>33</v>
       </c>
@@ -58421,7 +58421,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="63" customHeight="1" spans="1:27">
+    <row r="63" ht="13.5" customHeight="1" spans="1:27">
       <c r="A63" s="15"/>
       <c r="B63" s="14">
         <v>2</v>
@@ -58504,7 +58504,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="64" customHeight="1" spans="1:27">
+    <row r="64" ht="13.5" customHeight="1" spans="1:27">
       <c r="A64" s="15"/>
       <c r="B64" s="14">
         <v>3</v>
@@ -58587,7 +58587,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="65" customHeight="1" spans="1:27">
+    <row r="65" ht="13.5" customHeight="1" spans="1:27">
       <c r="A65" s="15"/>
       <c r="B65" s="16">
         <v>4</v>
@@ -58670,7 +58670,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="66" customHeight="1" spans="1:27">
+    <row r="66" ht="13.5" customHeight="1" spans="1:27">
       <c r="A66" s="15"/>
       <c r="B66" s="16">
         <v>5</v>
@@ -58753,7 +58753,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="67" customHeight="1" spans="1:27">
+    <row r="67" ht="13.5" customHeight="1" spans="1:27">
       <c r="A67" s="15"/>
       <c r="B67" s="16">
         <v>6</v>
@@ -58836,7 +58836,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="68" customHeight="1" spans="1:27">
+    <row r="68" ht="13.5" customHeight="1" spans="1:27">
       <c r="C68">
         <f>AVERAGE(C62:C67)</f>
         <v>5</v>
@@ -58938,8 +58938,8 @@
         <v>71.6666666666667</v>
       </c>
     </row>
-    <row r="69" customHeight="1"/>
-    <row r="70" customHeight="1" spans="1:27">
+    <row r="69" ht="13.5" customHeight="1"/>
+    <row r="70" ht="13.5" customHeight="1" spans="1:27">
       <c r="A70" s="20" t="s">
         <v>34</v>
       </c>
@@ -59024,7 +59024,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="71" customFormat="1" customHeight="1" spans="1:27">
+    <row r="71" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A71" s="28"/>
       <c r="B71" s="22">
         <v>13</v>
@@ -59107,7 +59107,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="72" customFormat="1" customHeight="1" spans="1:27">
+    <row r="72" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A72" s="28"/>
       <c r="B72" s="22">
         <v>14</v>
@@ -59190,7 +59190,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="73" customFormat="1" customHeight="1" spans="1:27">
+    <row r="73" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A73" s="28"/>
       <c r="B73" s="22">
         <v>15</v>
@@ -59273,7 +59273,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="74" customFormat="1" customHeight="1" spans="1:27">
+    <row r="74" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A74" s="28"/>
       <c r="B74" s="22">
         <v>16</v>
@@ -59356,7 +59356,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="75" customFormat="1" customHeight="1" spans="1:27">
+    <row r="75" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A75" s="28"/>
       <c r="B75" s="22">
         <v>17</v>
@@ -59439,7 +59439,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="76" customFormat="1" customHeight="1" spans="1:27">
+    <row r="76" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A76" s="28"/>
       <c r="B76" s="22">
         <v>18</v>
@@ -59522,7 +59522,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="77" customFormat="1" customHeight="1" spans="1:27">
+    <row r="77" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A77" s="28"/>
       <c r="B77" s="22">
         <v>19</v>
@@ -59605,7 +59605,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="78" customFormat="1" customHeight="1" spans="1:27">
+    <row r="78" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A78" s="28"/>
       <c r="B78" s="23">
         <v>9</v>
@@ -59688,7 +59688,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="79" customFormat="1" customHeight="1" spans="1:27">
+    <row r="79" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A79" s="31"/>
       <c r="B79" s="23">
         <v>10</v>
@@ -59771,7 +59771,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="80" customFormat="1" customHeight="1" spans="1:27">
+    <row r="80" customFormat="1" ht="13.5" customHeight="1" spans="1:27">
       <c r="A80" s="31"/>
       <c r="B80" s="23">
         <v>11</v>
@@ -59854,7 +59854,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="81" customHeight="1" spans="3:27">
+    <row r="81" ht="13.5" customHeight="1" spans="3:27">
       <c r="C81">
         <f>AVERAGE(C70:C80)</f>
         <v>5</v>

--- a/plot/data/raw/expert_rating_workbooks/专家3-专家评分——统计版.xlsx
+++ b/plot/data/raw/expert_rating_workbooks/专家3-专家评分——统计版.xlsx
@@ -117,7 +117,7 @@
     <t>答案解析评分</t>
   </si>
   <si>
-    <t>LLM总分</t>
+    <t>ULM总分</t>
   </si>
   <si>
     <t>该题是否为AI题</t>
